--- a/IngSoftware/propuesta/CasosDeTests/CasosTest-Gestionar Producto.xlsx
+++ b/IngSoftware/propuesta/CasosDeTests/CasosTest-Gestionar Producto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\source\TrabajoFinalAus\IngSoftware\propuesta\CasosDeTests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4432859C-95C9-433D-9FA8-B16A2F871F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1597563E-A862-4A13-855B-209438EC399E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="14" xr2:uid="{907B4683-9A02-4D8C-B9E2-85A5E705A97A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="7" xr2:uid="{907B4683-9A02-4D8C-B9E2-85A5E705A97A}"/>
   </bookViews>
   <sheets>
     <sheet name="7A-CASO FELIZ" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="7DM_14E-CATEGORIA" sheetId="20" r:id="rId13"/>
     <sheet name="7EM_14G-DESHABILITAR" sheetId="21" r:id="rId14"/>
     <sheet name="7FM_14G-DESHABILITAR ERRORES" sheetId="22" r:id="rId15"/>
+    <sheet name="7FM_14G-REHABILITAR" sheetId="27" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="100">
   <si>
     <t>N/A</t>
   </si>
@@ -390,6 +391,42 @@
   </si>
   <si>
     <t>Se abre un nuevo formulario para la modificacion.</t>
+  </si>
+  <si>
+    <t>El Producto se modifica.</t>
+  </si>
+  <si>
+    <t>* Descripcion = Repetir pruebas 7AM
+* Cantidad = Repetir prueba 7CM y 7FM
+* Categoria = Repetir prueba 7DM
+* Habilitar  = TRUE</t>
+  </si>
+  <si>
+    <t>* Existe una categoria de Productos final habilitada llamada "Tortas de Chocolate".
+* Existe al menos un Producto llamado "Torta de Chocolate"</t>
+  </si>
+  <si>
+    <t>* Existe una categoria de Productos final habilitada llamada "Tortas de Chocolate".
+* Existe al menos un Producto deshabilitado llamado "Torta de Chocolate"</t>
+  </si>
+  <si>
+    <t>El Sistema descarta la accion e  indica los errores que el campo de Categoria tiene.
+El Sistema permite realizar modificaciones al formulario y enviarlo nuevamente.</t>
+  </si>
+  <si>
+    <t>Se selecciona la opcion de 'Modificar Producto'</t>
+  </si>
+  <si>
+    <t>* Existe un producto llamado "Brownie de Coco" dado de alta.</t>
+  </si>
+  <si>
+    <t>Filtro = "Brownie de Coco"</t>
+  </si>
+  <si>
+    <t>Se utiliza el filtro por Nombre de producto y se selecciona el producto.</t>
+  </si>
+  <si>
+    <t>El producto queda seleccionado.</t>
   </si>
 </sst>
 </file>
@@ -431,7 +468,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -467,11 +504,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -522,20 +572,24 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="150">
+  <dxfs count="160">
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -623,9 +677,7 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -646,30 +698,30 @@
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -701,9 +753,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -791,9 +841,7 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -820,29 +868,29 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -908,6 +956,950 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -946,50 +1938,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -1388,23 +2336,23 @@
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -1414,7 +2362,7 @@
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -1602,6 +2550,50 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -1727,7 +2719,9 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1815,783 +2809,9 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -3007,136 +3227,153 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6E43AC89-0E5C-4246-B8B3-33610FC8FE6B}" name="Table2" displayName="Table2" ref="A7:E11" totalsRowShown="0" headerRowDxfId="139" dataDxfId="137" headerRowBorderDxfId="138" tableBorderDxfId="136" totalsRowBorderDxfId="135">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6E43AC89-0E5C-4246-B8B3-33610FC8FE6B}" name="Table2" displayName="Table2" ref="A7:E11" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146" totalsRowBorderDxfId="145">
   <autoFilter ref="A7:E11" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{24A6AD19-968B-4D0F-B19E-91A01420FF78}" name="Numero de Paso" dataDxfId="134"/>
-    <tableColumn id="2" xr3:uid="{D4259866-411E-40F1-898D-D467FD215EC2}" name="Accion" dataDxfId="133"/>
-    <tableColumn id="8" xr3:uid="{8129C9E6-1924-4286-A6C2-3EEBE58E3A1E}" name="Entrada" dataDxfId="132">
+    <tableColumn id="1" xr3:uid="{24A6AD19-968B-4D0F-B19E-91A01420FF78}" name="Numero de Paso" dataDxfId="144"/>
+    <tableColumn id="2" xr3:uid="{D4259866-411E-40F1-898D-D467FD215EC2}" name="Accion" dataDxfId="143"/>
+    <tableColumn id="8" xr3:uid="{8129C9E6-1924-4286-A6C2-3EEBE58E3A1E}" name="Entrada" dataDxfId="142">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0B1663DB-C235-4B08-86E1-8189BABE6031}" name="Resultados Esperados" dataDxfId="131"/>
-    <tableColumn id="6" xr3:uid="{CE6EDC0F-1D3F-474B-947A-9682A43024E4}" name="Resultados Obtenidos" dataDxfId="130"/>
+    <tableColumn id="5" xr3:uid="{0B1663DB-C235-4B08-86E1-8189BABE6031}" name="Resultados Esperados" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{CE6EDC0F-1D3F-474B-947A-9682A43024E4}" name="Resultados Obtenidos" dataDxfId="140"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ED63C8F8-D37D-47CE-8ABD-CD0B4463535B}" name="Table237" displayName="Table237" ref="A7:E11" totalsRowShown="0" headerRowDxfId="71" dataDxfId="69" headerRowBorderDxfId="70" tableBorderDxfId="68" totalsRowBorderDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ED63C8F8-D37D-47CE-8ABD-CD0B4463535B}" name="Table237" displayName="Table237" ref="A7:E11" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
   <autoFilter ref="A7:E11" xr:uid="{C90AE16F-5A5B-4C33-98F9-81888664F067}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{AA442F05-005C-40A9-AF0E-840349970DA6}" name="Numero de Paso" dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{9BA3DA2D-A64B-49FD-84F5-8B9CECDA8C94}" name="Accion" dataDxfId="65"/>
-    <tableColumn id="8" xr3:uid="{7398C574-FB08-460A-A65C-353BEBED56AA}" name="Entrada" dataDxfId="64">
+    <tableColumn id="1" xr3:uid="{AA442F05-005C-40A9-AF0E-840349970DA6}" name="Numero de Paso" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{9BA3DA2D-A64B-49FD-84F5-8B9CECDA8C94}" name="Accion" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{7398C574-FB08-460A-A65C-353BEBED56AA}" name="Entrada" dataDxfId="52">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{941E312F-F05B-429C-AB3D-90CF6EBCE95F}" name="Resultados Esperados" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{640ED3EC-3D10-4853-8009-D804778E1055}" name="Resultados Obtenidos" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{941E312F-F05B-429C-AB3D-90CF6EBCE95F}" name="Resultados Esperados" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{640ED3EC-3D10-4853-8009-D804778E1055}" name="Resultados Obtenidos" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{49F79B8B-08F5-4AB8-8D1B-1DDF7D526A39}" name="Table23711" displayName="Table23711" ref="A7:E11" totalsRowShown="0" headerRowDxfId="63" dataDxfId="61" headerRowBorderDxfId="62" tableBorderDxfId="60" totalsRowBorderDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{49F79B8B-08F5-4AB8-8D1B-1DDF7D526A39}" name="Table23711" displayName="Table23711" ref="A7:E11" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
   <autoFilter ref="A7:E11" xr:uid="{047A055C-AF14-422C-8FB3-A5F122E33821}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{71B3CDAA-B918-4BCA-8198-1506AA5B8403}" name="Numero de Paso" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{C9FDA1F6-771C-401E-B2B8-CFB5782D5C0E}" name="Accion" dataDxfId="57"/>
-    <tableColumn id="8" xr3:uid="{1CBA1EAE-64C5-42C3-9598-C1F89C90CF37}" name="Entrada" dataDxfId="56">
+    <tableColumn id="1" xr3:uid="{71B3CDAA-B918-4BCA-8198-1506AA5B8403}" name="Numero de Paso" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{C9FDA1F6-771C-401E-B2B8-CFB5782D5C0E}" name="Accion" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{1CBA1EAE-64C5-42C3-9598-C1F89C90CF37}" name="Entrada" dataDxfId="42">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{995A4BB6-32D9-4A09-BDC0-63C82DD67204}" name="Resultados Esperados" dataDxfId="55"/>
-    <tableColumn id="6" xr3:uid="{10197ADB-2E56-4276-8430-52F0FE788BE3}" name="Resultados Obtenidos" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{995A4BB6-32D9-4A09-BDC0-63C82DD67204}" name="Resultados Esperados" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{10197ADB-2E56-4276-8430-52F0FE788BE3}" name="Resultados Obtenidos" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{CA7E955E-0A86-4947-B5C6-2613E55F6518}" name="Table237113" displayName="Table237113" ref="A7:E11" totalsRowShown="0" headerRowDxfId="53" dataDxfId="51" headerRowBorderDxfId="52" tableBorderDxfId="50" totalsRowBorderDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{CA7E955E-0A86-4947-B5C6-2613E55F6518}" name="Table237113" displayName="Table237113" ref="A7:E11" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36" totalsRowBorderDxfId="35">
   <autoFilter ref="A7:E11" xr:uid="{047A055C-AF14-422C-8FB3-A5F122E33821}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{69635C28-33DC-4282-AC1B-B502C94BEA3F}" name="Numero de Paso" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{55FDD76C-5C72-42A1-8794-690B8A92F318}" name="Accion" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{3C3840B1-1401-479C-84D3-436E5D745040}" name="Entrada" dataDxfId="46">
+    <tableColumn id="1" xr3:uid="{69635C28-33DC-4282-AC1B-B502C94BEA3F}" name="Numero de Paso" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{55FDD76C-5C72-42A1-8794-690B8A92F318}" name="Accion" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{3C3840B1-1401-479C-84D3-436E5D745040}" name="Entrada" dataDxfId="32">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3835C49B-BA3E-4A92-8F9D-95908326A3AC}" name="Resultados Esperados" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{3302F39D-C94D-4D64-9A08-BDAFF33AFF3B}" name="Resultados Obtenidos" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{3835C49B-BA3E-4A92-8F9D-95908326A3AC}" name="Resultados Esperados" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{3302F39D-C94D-4D64-9A08-BDAFF33AFF3B}" name="Resultados Obtenidos" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{6CA2A938-6402-4F0E-9A05-83B05A07661E}" name="Table2312" displayName="Table2312" ref="A7:E11" totalsRowShown="0" headerRowDxfId="43" dataDxfId="41" headerRowBorderDxfId="42" tableBorderDxfId="40" totalsRowBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{6CA2A938-6402-4F0E-9A05-83B05A07661E}" name="Table2312" displayName="Table2312" ref="A7:E11" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
   <autoFilter ref="A7:E11" xr:uid="{25F65397-1E5C-40A2-8FC2-BB0E208A177E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{72CA698B-5567-4FE9-BE4A-5F369193357D}" name="Numero de Paso" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{E92C36AB-D96C-4146-A28D-E74F33897E00}" name="Accion" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{468D170D-611A-46E4-9012-22E2C94BD306}" name="Entrada" dataDxfId="36">
+    <tableColumn id="1" xr3:uid="{72CA698B-5567-4FE9-BE4A-5F369193357D}" name="Numero de Paso" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{E92C36AB-D96C-4146-A28D-E74F33897E00}" name="Accion" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{468D170D-611A-46E4-9012-22E2C94BD306}" name="Entrada" dataDxfId="22">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{2DDEC849-A79A-40F3-8BFA-F1A3D5ED281A}" name="Resultados Esperados" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{38B93C53-6888-4BD8-936A-340E074515FF}" name="Resultados Obtenidos" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{2DDEC849-A79A-40F3-8BFA-F1A3D5ED281A}" name="Resultados Esperados" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{38B93C53-6888-4BD8-936A-340E074515FF}" name="Resultados Obtenidos" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E523467A-E8B6-4FF2-8C8F-3CDCDB05E1F9}" name="Table231214" displayName="Table231214" ref="A7:E11" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E523467A-E8B6-4FF2-8C8F-3CDCDB05E1F9}" name="Table231214" displayName="Table231214" ref="A7:E11" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A7:E11" xr:uid="{E85131F1-E4F8-4567-9E28-46F38594088C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{96C7221F-0868-45C1-B43C-AE675BFB9E1C}" name="Numero de Paso" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{63E5C869-25BF-41CC-95B4-3A1DBC1F2679}" name="Accion" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{D0357635-7DA4-4723-8FCA-29E6A91BB2B8}" name="Entrada" dataDxfId="26">
+    <tableColumn id="1" xr3:uid="{96C7221F-0868-45C1-B43C-AE675BFB9E1C}" name="Numero de Paso" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{63E5C869-25BF-41CC-95B4-3A1DBC1F2679}" name="Accion" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{D0357635-7DA4-4723-8FCA-29E6A91BB2B8}" name="Entrada" dataDxfId="12">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{09BD5A8E-411B-4D50-A50F-7DC071E009B2}" name="Resultados Esperados" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{3D19E504-2712-484C-92BD-DF8EDF1FF518}" name="Resultados Obtenidos" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{09BD5A8E-411B-4D50-A50F-7DC071E009B2}" name="Resultados Esperados" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{3D19E504-2712-484C-92BD-DF8EDF1FF518}" name="Resultados Obtenidos" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{1AB929E7-0467-42AE-B56F-5F3CA83583BD}" name="Table2312142" displayName="Table2312142" ref="A7:E11" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146" totalsRowBorderDxfId="145">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{1AB929E7-0467-42AE-B56F-5F3CA83583BD}" name="Table2312142" displayName="Table2312142" ref="A7:E11" totalsRowShown="0" headerRowDxfId="159" dataDxfId="157" headerRowBorderDxfId="158" tableBorderDxfId="156" totalsRowBorderDxfId="155">
   <autoFilter ref="A7:E11" xr:uid="{E85131F1-E4F8-4567-9E28-46F38594088C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F731284F-0480-4539-9750-F5A24EB62699}" name="Numero de Paso" dataDxfId="144"/>
-    <tableColumn id="2" xr3:uid="{619307C9-70F9-432E-9C0C-5D1310C7E0CC}" name="Accion" dataDxfId="143"/>
-    <tableColumn id="8" xr3:uid="{5AFDC811-C251-4B05-B6FE-26CE34C1CA52}" name="Entrada" dataDxfId="142">
+    <tableColumn id="1" xr3:uid="{F731284F-0480-4539-9750-F5A24EB62699}" name="Numero de Paso" dataDxfId="154"/>
+    <tableColumn id="2" xr3:uid="{619307C9-70F9-432E-9C0C-5D1310C7E0CC}" name="Accion" dataDxfId="153"/>
+    <tableColumn id="8" xr3:uid="{5AFDC811-C251-4B05-B6FE-26CE34C1CA52}" name="Entrada" dataDxfId="152">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C16BEA45-3146-4ED3-943F-E34C651B0BA2}" name="Resultados" dataDxfId="141"/>
-    <tableColumn id="6" xr3:uid="{C574AB58-D021-4E7B-8CB4-41AD3B373F6B}" name="Comentarios" dataDxfId="140"/>
+    <tableColumn id="5" xr3:uid="{C16BEA45-3146-4ED3-943F-E34C651B0BA2}" name="Resultados" dataDxfId="151"/>
+    <tableColumn id="6" xr3:uid="{C574AB58-D021-4E7B-8CB4-41AD3B373F6B}" name="Comentarios" dataDxfId="150"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{3FF9DF0C-32BE-4347-984C-A09794CCD4F2}" name="Table231214217" displayName="Table231214217" ref="A7:E11" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+  <autoFilter ref="A7:E11" xr:uid="{E85131F1-E4F8-4567-9E28-46F38594088C}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{4324B215-E039-4F8E-BDCE-B13F8FC97B83}" name="Numero de Paso" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{604AE212-AB7F-466A-846D-5851418040AB}" name="Accion" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{707791EE-F2EB-4590-B328-93D7258BD8AE}" name="Entrada" dataDxfId="2">
+      <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
+- Cantidad = "1"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{F3B23BB8-D37A-4239-AF1B-DC05FAA1CAE9}" name="Resultados" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{F187C750-B74D-4FF9-8E3E-1783F252F0C7}" name="Comentarios" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3FAAF92A-2C8D-40DC-8A23-DD6A81E81F02}" name="Table215" displayName="Table215" ref="A7:E10" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3FAAF92A-2C8D-40DC-8A23-DD6A81E81F02}" name="Table215" displayName="Table215" ref="A7:E10" totalsRowShown="0" headerRowDxfId="139" dataDxfId="137" headerRowBorderDxfId="138" tableBorderDxfId="136" totalsRowBorderDxfId="135">
   <autoFilter ref="A7:E10" xr:uid="{3FAAF92A-2C8D-40DC-8A23-DD6A81E81F02}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{27A0B040-AA3E-4B05-8B4F-0EA2E64AE54A}" name="Numero de Paso" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{9E9176B7-2B18-4676-B8FF-05D61600B85F}" name="Accion" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{53F450CC-4F2B-4194-A7EA-4264D1CB2C45}" name="Entrada" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{27A0B040-AA3E-4B05-8B4F-0EA2E64AE54A}" name="Numero de Paso" dataDxfId="134"/>
+    <tableColumn id="2" xr3:uid="{9E9176B7-2B18-4676-B8FF-05D61600B85F}" name="Accion" dataDxfId="133"/>
+    <tableColumn id="8" xr3:uid="{53F450CC-4F2B-4194-A7EA-4264D1CB2C45}" name="Entrada" dataDxfId="132">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7481430F-57D2-4BB4-83FA-DF2B69ED8D12}" name="Resultados Esperados" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{826F56AE-21A3-4821-AC1F-046FE9FB74C6}" name="Resultados Obtenidos" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{7481430F-57D2-4BB4-83FA-DF2B69ED8D12}" name="Resultados Esperados" dataDxfId="131"/>
+    <tableColumn id="6" xr3:uid="{826F56AE-21A3-4821-AC1F-046FE9FB74C6}" name="Resultados Obtenidos" dataDxfId="130"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3220,42 +3457,42 @@
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{10D03F6A-3B48-4B4C-AB1F-7C834555A22F}" name="Resultados Esperados" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{77D52C61-7D1E-4505-879C-C2D7C8374B79}" name="Resultados Obtenidos" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{10D03F6A-3B48-4B4C-AB1F-7C834555A22F}" name="Resultados Esperados" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{77D52C61-7D1E-4505-879C-C2D7C8374B79}" name="Resultados Obtenidos" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{815EF42E-D784-4219-AD3C-9AC949D530D1}" name="Table236" displayName="Table236" ref="A7:E11" totalsRowShown="0" headerRowDxfId="81" dataDxfId="79" headerRowBorderDxfId="80" tableBorderDxfId="78" totalsRowBorderDxfId="77">
-  <autoFilter ref="A7:E11" xr:uid="{715B9BAD-1497-41F0-B764-45044D3C92AC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{815EF42E-D784-4219-AD3C-9AC949D530D1}" name="Table236" displayName="Table236" ref="A7:E12" totalsRowShown="0" headerRowDxfId="79" dataDxfId="77" headerRowBorderDxfId="78" tableBorderDxfId="76" totalsRowBorderDxfId="75">
+  <autoFilter ref="A7:E12" xr:uid="{715B9BAD-1497-41F0-B764-45044D3C92AC}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A93CF38D-7DFE-4F9A-9377-898DFF943F87}" name="Numero de Paso" dataDxfId="76"/>
-    <tableColumn id="2" xr3:uid="{0702067E-FD3D-44DC-9E82-1D0504306ED4}" name="Accion" dataDxfId="75"/>
-    <tableColumn id="8" xr3:uid="{7C9F77C2-31E9-4117-A7A2-F7356C3FC7AE}" name="Entrada" dataDxfId="74">
+    <tableColumn id="1" xr3:uid="{A93CF38D-7DFE-4F9A-9377-898DFF943F87}" name="Numero de Paso" dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{0702067E-FD3D-44DC-9E82-1D0504306ED4}" name="Accion" dataDxfId="73"/>
+    <tableColumn id="8" xr3:uid="{7C9F77C2-31E9-4117-A7A2-F7356C3FC7AE}" name="Entrada" dataDxfId="72">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7AD3CC43-D1D7-4195-9746-65A7A8FD220B}" name="Resultados Esperados" dataDxfId="73"/>
-    <tableColumn id="6" xr3:uid="{986A7CE9-EF2E-40D3-A217-09C2FB7B25F3}" name="Resultados Obtenidos" dataDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{7AD3CC43-D1D7-4195-9746-65A7A8FD220B}" name="Resultados Esperados" dataDxfId="71"/>
+    <tableColumn id="6" xr3:uid="{986A7CE9-EF2E-40D3-A217-09C2FB7B25F3}" name="Resultados Obtenidos" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{F7D47040-4A05-469E-8772-1E419830AEB8}" name="Table21516" displayName="Table21516" ref="A7:E10" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{F7D47040-4A05-469E-8772-1E419830AEB8}" name="Table21516" displayName="Table21516" ref="A7:E10" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68" tableBorderDxfId="66" totalsRowBorderDxfId="65">
   <autoFilter ref="A7:E10" xr:uid="{F7D47040-4A05-469E-8772-1E419830AEB8}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F771E58E-D809-4572-8829-3A29D4FCE3F4}" name="Numero de Paso" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{B6101E35-03D2-49CE-B842-062C4A8AE380}" name="Accion" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{D94708F2-1E8F-4E64-AC2B-1D38C72768E1}" name="Entrada" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{F771E58E-D809-4572-8829-3A29D4FCE3F4}" name="Numero de Paso" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{B6101E35-03D2-49CE-B842-062C4A8AE380}" name="Accion" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{D94708F2-1E8F-4E64-AC2B-1D38C72768E1}" name="Entrada" dataDxfId="62">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{563F58D4-687D-4394-B151-C791528C0ECF}" name="Resultados Esperados" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{B9462076-3482-4FF0-8B86-2B5D3DE49305}" name="Resultados Obtenidos" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{563F58D4-687D-4394-B151-C791528C0ECF}" name="Resultados Esperados" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{B9462076-3482-4FF0-8B86-2B5D3DE49305}" name="Resultados Obtenidos" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4214,7 +4451,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>0</v>
@@ -4387,7 +4624,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>0</v>
@@ -4423,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -4436,8 +4673,9 @@
     <mergeCell ref="A5:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4492,13 +4730,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="4" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>8</v>
@@ -4770,6 +5008,179 @@
       </c>
       <c r="D11" s="2" t="s">
         <v>70</v>
+      </c>
+      <c r="E11" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:E6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576B818F-F28E-40A4-B9A6-949AC65F1FEB}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="4">
+        <v>7</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -5840,7 +6251,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49B773F1-27C7-44CC-8EC9-9C55B5034F40}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.28515625" customWidth="1"/>
@@ -5894,7 +6305,7 @@
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="4" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
@@ -5951,50 +6362,65 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+    <row r="9" spans="1:5" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" s="18">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="1"/>
+      <c r="E12" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/IngSoftware/propuesta/CasosDeTests/CasosTest-Gestionar Producto.xlsx
+++ b/IngSoftware/propuesta/CasosDeTests/CasosTest-Gestionar Producto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\source\TrabajoFinalAus\IngSoftware\propuesta\CasosDeTests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1597563E-A862-4A13-855B-209438EC399E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FA9FDA-3201-48E8-843C-9F9DC0CE7851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="7" xr2:uid="{907B4683-9A02-4D8C-B9E2-85A5E705A97A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="14" xr2:uid="{907B4683-9A02-4D8C-B9E2-85A5E705A97A}"/>
   </bookViews>
   <sheets>
     <sheet name="7A-CASO FELIZ" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,7 @@
     <sheet name="7FM_14B-CANTIDAD ERROR UNIDAD" sheetId="19" r:id="rId12"/>
     <sheet name="7DM_14E-CATEGORIA" sheetId="20" r:id="rId13"/>
     <sheet name="7EM_14G-DESHABILITAR" sheetId="21" r:id="rId14"/>
-    <sheet name="7FM_14G-DESHABILITAR ERRORES" sheetId="22" r:id="rId15"/>
-    <sheet name="7FM_14G-REHABILITAR" sheetId="27" r:id="rId16"/>
+    <sheet name="7GM_14G-REHABILITAR" sheetId="27" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="98">
   <si>
     <t>N/A</t>
   </si>
@@ -209,12 +208,6 @@
     <t>El Sistema descarta la accion e  indica mediante una leyenda que debe darse de alta al menos una Unidad.</t>
   </si>
   <si>
-    <t>* Descripcion = "Torta de Chocolate tipo Matilda"
-* Cantidad = "1"
-* Categoria = "Tortas de Chocolate"
-* Habilitar  = TRUE</t>
-  </si>
-  <si>
     <t>El Producto NO se modifica indicando el error.</t>
   </si>
   <si>
@@ -224,26 +217,7 @@
     <t>7AM</t>
   </si>
   <si>
-    <t>* Descripcion = Cadena muy corta, muy larga o vacia.
-* Cantidad = "1"
-* Categoria = "Tortas de Chocolate"
-* Habilitar  = TRUE</t>
-  </si>
-  <si>
-    <t>* Existe una categoria de Productos final habilitada llamada "Tortas de Chocolate"</t>
-  </si>
-  <si>
     <t>Modificacion de  Producto: Error en nombre.</t>
-  </si>
-  <si>
-    <t>* Descripcion = "Torta Tipo Matilda"
-* Cantidad = Cantidad vacia, con mal formato, negativa, o no se condice con la unidad. 
-Por ejemplo: "1xebc", "-1", "", "1.1" .
-* Categoria = "Tortas de Chocolate"
-* Habilitar  = TRUE</t>
-  </si>
-  <si>
-    <t>* Existe una categoria de Productos final habilitada llamada "Tortas de Chocolate".</t>
   </si>
   <si>
     <t>Modificacion de  Producto: Error en cantidad.</t>
@@ -257,10 +231,6 @@
 * Habilitar  = TRUE</t>
   </si>
   <si>
-    <t>* Existe una categoria de Productos final habilitada llamada "Tortas de Chocolate".
-* La Unidad del Producto maneja cantidades enteras o flotantes.</t>
-  </si>
-  <si>
     <t>Modificacion de  Producto: Error en la categoria.</t>
   </si>
   <si>
@@ -274,12 +244,6 @@
   </si>
   <si>
     <t>Modificacion de  Producto: Baja de producto.</t>
-  </si>
-  <si>
-    <t>* Descripcion = Repetir pruebas 7AM
-* Cantidad = Repetir prueba 7CM y 7FM
-* Categoria = Repetir prueba 7DM
-* Habilitar  = FALSE</t>
   </si>
   <si>
     <t>Modificacion de  Producto: Baja de producto, con errores.</t>
@@ -323,10 +287,6 @@
 El Sistema permite realizar modificaciones al formulario y enviarlo nuevamente.</t>
   </si>
   <si>
-    <t>El Sistema descarta la accion e  indica los errores que los distintos campos tienen.
-El Sistema permite realizar modificaciones al formulario y enviarlo nuevamente.</t>
-  </si>
-  <si>
     <t>El Sistema descarta la accion e  indica los errores que el campo Cantidad tiene.
 El Sistema permite realizar modificaciones al formulario y enviarlo nuevamente.</t>
   </si>
@@ -396,20 +356,6 @@
     <t>El Producto se modifica.</t>
   </si>
   <si>
-    <t>* Descripcion = Repetir pruebas 7AM
-* Cantidad = Repetir prueba 7CM y 7FM
-* Categoria = Repetir prueba 7DM
-* Habilitar  = TRUE</t>
-  </si>
-  <si>
-    <t>* Existe una categoria de Productos final habilitada llamada "Tortas de Chocolate".
-* Existe al menos un Producto llamado "Torta de Chocolate"</t>
-  </si>
-  <si>
-    <t>* Existe una categoria de Productos final habilitada llamada "Tortas de Chocolate".
-* Existe al menos un Producto deshabilitado llamado "Torta de Chocolate"</t>
-  </si>
-  <si>
     <t>El Sistema descarta la accion e  indica los errores que el campo de Categoria tiene.
 El Sistema permite realizar modificaciones al formulario y enviarlo nuevamente.</t>
   </si>
@@ -427,6 +373,50 @@
   </si>
   <si>
     <t>El producto queda seleccionado.</t>
+  </si>
+  <si>
+    <t>Filtro = "Torta de Chocolate"</t>
+  </si>
+  <si>
+    <t>* Existe una categoria de Productos final habilitada llamada "Torta de Chocolate"</t>
+  </si>
+  <si>
+    <t>* Descripcion = "Brownie de Coco"
+* Cantidad = Cantidad vacia, con mal formato, negativa, o no se condice con la unidad. 
+Por ejemplo: "1xebc", "-1", "", "1.1" .
+* Categoria = "Brownies"
+* Habilitar  = TRUE</t>
+  </si>
+  <si>
+    <t>* Descripcion = Cadena muy corta, muy larga o vacia.
+* Cantidad = "1"
+* Categoria = "Brownies"
+* Habilitar  = TRUE</t>
+  </si>
+  <si>
+    <t>* Existe un producto llamado "Brownie de Coco" dado de alta.
+*Existe una categoria final habilitada llamada "Brownies".</t>
+  </si>
+  <si>
+    <t>* Existe un producto llamado "Torta de Chocolate" dado de alta.
+* Existe una categoria final habilitada llamada "Tortas de Chocolate".
+* La Unidad del Producto maneja cantidades enteras o flotantes.</t>
+  </si>
+  <si>
+    <t>* Existe un producto llamado "Torta de Chocolate" dado de alta.
+* Existe una categoria final habilitada llamada "Tortas de Chocolate".</t>
+  </si>
+  <si>
+    <t>* Descripcion = "Brownie de vainilla con glaseado y topping de coco"
+* Cantidad = "1"
+* Categoria = "Tortas de Chocolate"
+* Habilitar  = TRUE</t>
+  </si>
+  <si>
+    <t>* Descripcion = "Torta de Chocolate tipo Matilda"
+* Cantidad = "1"
+* Categoria = "Tortas de chocolate"
+* Habilitar  = TRUE</t>
   </si>
 </sst>
 </file>
@@ -521,7 +511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -560,29 +550,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="160">
+  <dxfs count="150">
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -698,30 +685,30 @@
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -862,23 +849,23 @@
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -888,7 +875,7 @@
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -3027,170 +3014,6 @@
       <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -3227,25 +3050,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6E43AC89-0E5C-4246-B8B3-33610FC8FE6B}" name="Table2" displayName="Table2" ref="A7:E11" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146" totalsRowBorderDxfId="145">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6E43AC89-0E5C-4246-B8B3-33610FC8FE6B}" name="Table2" displayName="Table2" ref="A7:E11" totalsRowShown="0" headerRowDxfId="139" dataDxfId="137" headerRowBorderDxfId="138" tableBorderDxfId="136" totalsRowBorderDxfId="135">
   <autoFilter ref="A7:E11" xr:uid="{4BA518DF-933C-430D-AE9D-A2679D3393B2}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{24A6AD19-968B-4D0F-B19E-91A01420FF78}" name="Numero de Paso" dataDxfId="144"/>
-    <tableColumn id="2" xr3:uid="{D4259866-411E-40F1-898D-D467FD215EC2}" name="Accion" dataDxfId="143"/>
-    <tableColumn id="8" xr3:uid="{8129C9E6-1924-4286-A6C2-3EEBE58E3A1E}" name="Entrada" dataDxfId="142">
+    <tableColumn id="1" xr3:uid="{24A6AD19-968B-4D0F-B19E-91A01420FF78}" name="Numero de Paso" dataDxfId="134"/>
+    <tableColumn id="2" xr3:uid="{D4259866-411E-40F1-898D-D467FD215EC2}" name="Accion" dataDxfId="133"/>
+    <tableColumn id="8" xr3:uid="{8129C9E6-1924-4286-A6C2-3EEBE58E3A1E}" name="Entrada" dataDxfId="132">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0B1663DB-C235-4B08-86E1-8189BABE6031}" name="Resultados Esperados" dataDxfId="141"/>
-    <tableColumn id="6" xr3:uid="{CE6EDC0F-1D3F-474B-947A-9682A43024E4}" name="Resultados Obtenidos" dataDxfId="140"/>
+    <tableColumn id="5" xr3:uid="{0B1663DB-C235-4B08-86E1-8189BABE6031}" name="Resultados Esperados" dataDxfId="131"/>
+    <tableColumn id="6" xr3:uid="{CE6EDC0F-1D3F-474B-947A-9682A43024E4}" name="Resultados Obtenidos" dataDxfId="130"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ED63C8F8-D37D-47CE-8ABD-CD0B4463535B}" name="Table237" displayName="Table237" ref="A7:E11" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
-  <autoFilter ref="A7:E11" xr:uid="{C90AE16F-5A5B-4C33-98F9-81888664F067}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ED63C8F8-D37D-47CE-8ABD-CD0B4463535B}" name="Table237" displayName="Table237" ref="A7:E12" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
+  <autoFilter ref="A7:E12" xr:uid="{C90AE16F-5A5B-4C33-98F9-81888664F067}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{AA442F05-005C-40A9-AF0E-840349970DA6}" name="Numero de Paso" dataDxfId="54"/>
     <tableColumn id="2" xr3:uid="{9BA3DA2D-A64B-49FD-84F5-8B9CECDA8C94}" name="Accion" dataDxfId="53"/>
@@ -3261,8 +3084,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{49F79B8B-08F5-4AB8-8D1B-1DDF7D526A39}" name="Table23711" displayName="Table23711" ref="A7:E11" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
-  <autoFilter ref="A7:E11" xr:uid="{047A055C-AF14-422C-8FB3-A5F122E33821}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{49F79B8B-08F5-4AB8-8D1B-1DDF7D526A39}" name="Table23711" displayName="Table23711" ref="A7:E12" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
+  <autoFilter ref="A7:E12" xr:uid="{047A055C-AF14-422C-8FB3-A5F122E33821}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{71B3CDAA-B918-4BCA-8198-1506AA5B8403}" name="Numero de Paso" dataDxfId="44"/>
     <tableColumn id="2" xr3:uid="{C9FDA1F6-771C-401E-B2B8-CFB5782D5C0E}" name="Accion" dataDxfId="43"/>
@@ -3278,8 +3101,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{CA7E955E-0A86-4947-B5C6-2613E55F6518}" name="Table237113" displayName="Table237113" ref="A7:E11" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36" totalsRowBorderDxfId="35">
-  <autoFilter ref="A7:E11" xr:uid="{047A055C-AF14-422C-8FB3-A5F122E33821}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{CA7E955E-0A86-4947-B5C6-2613E55F6518}" name="Table237113" displayName="Table237113" ref="A7:E12" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36" totalsRowBorderDxfId="35">
+  <autoFilter ref="A7:E12" xr:uid="{047A055C-AF14-422C-8FB3-A5F122E33821}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{69635C28-33DC-4282-AC1B-B502C94BEA3F}" name="Numero de Paso" dataDxfId="34"/>
     <tableColumn id="2" xr3:uid="{55FDD76C-5C72-42A1-8794-690B8A92F318}" name="Accion" dataDxfId="33"/>
@@ -3295,8 +3118,8 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{6CA2A938-6402-4F0E-9A05-83B05A07661E}" name="Table2312" displayName="Table2312" ref="A7:E11" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
-  <autoFilter ref="A7:E11" xr:uid="{25F65397-1E5C-40A2-8FC2-BB0E208A177E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{6CA2A938-6402-4F0E-9A05-83B05A07661E}" name="Table2312" displayName="Table2312" ref="A7:E12" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
+  <autoFilter ref="A7:E12" xr:uid="{25F65397-1E5C-40A2-8FC2-BB0E208A177E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{72CA698B-5567-4FE9-BE4A-5F369193357D}" name="Numero de Paso" dataDxfId="24"/>
     <tableColumn id="2" xr3:uid="{E92C36AB-D96C-4146-A28D-E74F33897E00}" name="Accion" dataDxfId="23"/>
@@ -3312,68 +3135,51 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E523467A-E8B6-4FF2-8C8F-3CDCDB05E1F9}" name="Table231214" displayName="Table231214" ref="A7:E11" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
-  <autoFilter ref="A7:E11" xr:uid="{E85131F1-E4F8-4567-9E28-46F38594088C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E523467A-E8B6-4FF2-8C8F-3CDCDB05E1F9}" name="Table231214" displayName="Table231214" ref="A7:E12" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+  <autoFilter ref="A7:E12" xr:uid="{E85131F1-E4F8-4567-9E28-46F38594088C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{96C7221F-0868-45C1-B43C-AE675BFB9E1C}" name="Numero de Paso" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{63E5C869-25BF-41CC-95B4-3A1DBC1F2679}" name="Accion" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{D0357635-7DA4-4723-8FCA-29E6A91BB2B8}" name="Entrada" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{96C7221F-0868-45C1-B43C-AE675BFB9E1C}" name="Numero de Paso" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{63E5C869-25BF-41CC-95B4-3A1DBC1F2679}" name="Accion" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{D0357635-7DA4-4723-8FCA-29E6A91BB2B8}" name="Entrada" dataDxfId="2">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{09BD5A8E-411B-4D50-A50F-7DC071E009B2}" name="Resultados Esperados" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{3D19E504-2712-484C-92BD-DF8EDF1FF518}" name="Resultados Obtenidos" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{09BD5A8E-411B-4D50-A50F-7DC071E009B2}" name="Resultados Esperados" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{3D19E504-2712-484C-92BD-DF8EDF1FF518}" name="Resultados Obtenidos" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{1AB929E7-0467-42AE-B56F-5F3CA83583BD}" name="Table2312142" displayName="Table2312142" ref="A7:E11" totalsRowShown="0" headerRowDxfId="159" dataDxfId="157" headerRowBorderDxfId="158" tableBorderDxfId="156" totalsRowBorderDxfId="155">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{3FF9DF0C-32BE-4347-984C-A09794CCD4F2}" name="Table231214217" displayName="Table231214217" ref="A7:E11" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A7:E11" xr:uid="{E85131F1-E4F8-4567-9E28-46F38594088C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F731284F-0480-4539-9750-F5A24EB62699}" name="Numero de Paso" dataDxfId="154"/>
-    <tableColumn id="2" xr3:uid="{619307C9-70F9-432E-9C0C-5D1310C7E0CC}" name="Accion" dataDxfId="153"/>
-    <tableColumn id="8" xr3:uid="{5AFDC811-C251-4B05-B6FE-26CE34C1CA52}" name="Entrada" dataDxfId="152">
+    <tableColumn id="1" xr3:uid="{4324B215-E039-4F8E-BDCE-B13F8FC97B83}" name="Numero de Paso" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{604AE212-AB7F-466A-846D-5851418040AB}" name="Accion" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{707791EE-F2EB-4590-B328-93D7258BD8AE}" name="Entrada" dataDxfId="12">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C16BEA45-3146-4ED3-943F-E34C651B0BA2}" name="Resultados" dataDxfId="151"/>
-    <tableColumn id="6" xr3:uid="{C574AB58-D021-4E7B-8CB4-41AD3B373F6B}" name="Comentarios" dataDxfId="150"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{3FF9DF0C-32BE-4347-984C-A09794CCD4F2}" name="Table231214217" displayName="Table231214217" ref="A7:E11" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
-  <autoFilter ref="A7:E11" xr:uid="{E85131F1-E4F8-4567-9E28-46F38594088C}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4324B215-E039-4F8E-BDCE-B13F8FC97B83}" name="Numero de Paso" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{604AE212-AB7F-466A-846D-5851418040AB}" name="Accion" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{707791EE-F2EB-4590-B328-93D7258BD8AE}" name="Entrada" dataDxfId="2">
-      <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
-- Cantidad = "1"</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{F3B23BB8-D37A-4239-AF1B-DC05FAA1CAE9}" name="Resultados" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{F187C750-B74D-4FF9-8E3E-1783F252F0C7}" name="Comentarios" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{F3B23BB8-D37A-4239-AF1B-DC05FAA1CAE9}" name="Resultados" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{F187C750-B74D-4FF9-8E3E-1783F252F0C7}" name="Comentarios" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3FAAF92A-2C8D-40DC-8A23-DD6A81E81F02}" name="Table215" displayName="Table215" ref="A7:E10" totalsRowShown="0" headerRowDxfId="139" dataDxfId="137" headerRowBorderDxfId="138" tableBorderDxfId="136" totalsRowBorderDxfId="135">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3FAAF92A-2C8D-40DC-8A23-DD6A81E81F02}" name="Table215" displayName="Table215" ref="A7:E10" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146" totalsRowBorderDxfId="145">
   <autoFilter ref="A7:E10" xr:uid="{3FAAF92A-2C8D-40DC-8A23-DD6A81E81F02}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{27A0B040-AA3E-4B05-8B4F-0EA2E64AE54A}" name="Numero de Paso" dataDxfId="134"/>
-    <tableColumn id="2" xr3:uid="{9E9176B7-2B18-4676-B8FF-05D61600B85F}" name="Accion" dataDxfId="133"/>
-    <tableColumn id="8" xr3:uid="{53F450CC-4F2B-4194-A7EA-4264D1CB2C45}" name="Entrada" dataDxfId="132">
+    <tableColumn id="1" xr3:uid="{27A0B040-AA3E-4B05-8B4F-0EA2E64AE54A}" name="Numero de Paso" dataDxfId="144"/>
+    <tableColumn id="2" xr3:uid="{9E9176B7-2B18-4676-B8FF-05D61600B85F}" name="Accion" dataDxfId="143"/>
+    <tableColumn id="8" xr3:uid="{53F450CC-4F2B-4194-A7EA-4264D1CB2C45}" name="Entrada" dataDxfId="142">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7481430F-57D2-4BB4-83FA-DF2B69ED8D12}" name="Resultados Esperados" dataDxfId="131"/>
-    <tableColumn id="6" xr3:uid="{826F56AE-21A3-4821-AC1F-046FE9FB74C6}" name="Resultados Obtenidos" dataDxfId="130"/>
+    <tableColumn id="5" xr3:uid="{7481430F-57D2-4BB4-83FA-DF2B69ED8D12}" name="Resultados Esperados" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{826F56AE-21A3-4821-AC1F-046FE9FB74C6}" name="Resultados Obtenidos" dataDxfId="140"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3826,19 +3632,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -3880,20 +3686,20 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -3989,7 +3795,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C94357D-4B8B-4069-8E95-5BA7D552E10A}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.5703125" customWidth="1"/>
@@ -3999,19 +3805,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -4019,7 +3825,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4028,7 +3834,7 @@
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
@@ -4043,30 +3849,30 @@
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="4" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -4101,49 +3907,64 @@
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>62</v>
+        <v>86</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="1"/>
+      <c r="D12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4162,7 +3983,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE0B44F7-6594-44AE-870D-EDB2D5C8327F}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -4172,19 +3993,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -4192,7 +4013,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -4201,7 +4022,7 @@
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
@@ -4216,30 +4037,30 @@
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="4" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -4274,49 +4095,64 @@
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>62</v>
+        <v>86</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="1"/>
+      <c r="D12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4335,7 +4171,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD4039FB-637D-41B4-9D1F-D9255627A80E}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -4345,19 +4181,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -4365,7 +4201,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -4374,7 +4210,7 @@
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
@@ -4383,36 +4219,36 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="4" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -4447,49 +4283,64 @@
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>62</v>
+        <v>89</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="1"/>
+      <c r="D12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4508,7 +4359,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729CB741-417B-40AD-BC21-C3249BB6C4E1}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="37.42578125" customWidth="1"/>
@@ -4518,19 +4369,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -4538,16 +4389,16 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="15"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>11</v>
@@ -4557,35 +4408,35 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="15"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="4" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -4619,50 +4470,65 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="1"/>
+      <c r="D12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4682,7 +4548,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43387705-F35A-43C8-B4A6-19D31406FDCE}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="29.42578125" customWidth="1"/>
@@ -4692,19 +4558,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -4712,16 +4578,16 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="15"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>11</v>
@@ -4731,35 +4597,35 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="15"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -4793,50 +4659,65 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="1"/>
+      <c r="D12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4854,179 +4735,6 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{648CF719-E74C-4ECC-8620-57D8944869FA}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-    </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="4">
-        <v>7</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:E6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576B818F-F28E-40A4-B9A6-949AC65F1FEB}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5038,19 +4746,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -5058,16 +4766,16 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="15"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>11</v>
@@ -5076,36 +4784,36 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="15"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -5150,11 +4858,11 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -5162,7 +4870,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>37</v>
@@ -5180,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -5212,19 +4920,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -5262,24 +4970,24 @@
         <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -5333,13 +5041,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E10" s="1"/>
     </row>
@@ -5373,21 +5081,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -5395,7 +5103,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
@@ -5435,22 +5143,22 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
     </row>
@@ -5569,19 +5277,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -5589,7 +5297,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5623,20 +5331,20 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -5742,19 +5450,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -5762,7 +5470,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5796,20 +5504,20 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -5866,7 +5574,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>37</v>
@@ -5884,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -5915,19 +5623,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -5935,7 +5643,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5969,20 +5677,20 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -6039,7 +5747,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>37</v>
@@ -6057,7 +5765,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -6088,19 +5796,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -6108,7 +5816,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6142,20 +5850,20 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -6212,7 +5920,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>37</v>
@@ -6230,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -6261,19 +5969,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -6281,7 +5989,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6290,7 +5998,7 @@
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
@@ -6305,30 +6013,30 @@
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="4" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -6363,17 +6071,17 @@
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
+      <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>97</v>
+        <v>87</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E9" s="1"/>
     </row>
@@ -6382,25 +6090,25 @@
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A11" s="18">
+      <c r="A11" s="14">
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>37</v>
@@ -6418,7 +6126,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -6449,19 +6157,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -6499,24 +6207,24 @@
         <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -6561,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E9" s="1"/>
     </row>
@@ -6570,13 +6278,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E10" s="1"/>
     </row>

--- a/IngSoftware/propuesta/CasosDeTests/CasosTest-Gestionar Producto.xlsx
+++ b/IngSoftware/propuesta/CasosDeTests/CasosTest-Gestionar Producto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\source\TrabajoFinalAus\IngSoftware\propuesta\CasosDeTests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eerojas\source\TrabajoFinalAus\IngSoftware\propuesta\CasosDeTests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FA9FDA-3201-48E8-843C-9F9DC0CE7851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CFD622C-6E5B-41CF-B174-D3D1DD932EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="14" xr2:uid="{907B4683-9A02-4D8C-B9E2-85A5E705A97A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="13" xr2:uid="{907B4683-9A02-4D8C-B9E2-85A5E705A97A}"/>
   </bookViews>
   <sheets>
     <sheet name="7A-CASO FELIZ" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="99">
   <si>
     <t>N/A</t>
   </si>
@@ -246,9 +246,6 @@
     <t>Modificacion de  Producto: Baja de producto.</t>
   </si>
   <si>
-    <t>Modificacion de  Producto: Baja de producto, con errores.</t>
-  </si>
-  <si>
     <t>Se abre un nuevo formulario para realizar la modificacion del producto.</t>
   </si>
   <si>
@@ -403,10 +400,6 @@
 * La Unidad del Producto maneja cantidades enteras o flotantes.</t>
   </si>
   <si>
-    <t>* Existe un producto llamado "Torta de Chocolate" dado de alta.
-* Existe una categoria final habilitada llamada "Tortas de Chocolate".</t>
-  </si>
-  <si>
     <t>* Descripcion = "Brownie de vainilla con glaseado y topping de coco"
 * Cantidad = "1"
 * Categoria = "Tortas de Chocolate"
@@ -417,13 +410,24 @@
 * Cantidad = "1"
 * Categoria = "Tortas de chocolate"
 * Habilitar  = TRUE</t>
+  </si>
+  <si>
+    <t>Modificacion de  Producto: Rehabilitar Producto.</t>
+  </si>
+  <si>
+    <t>* Existe un producto llamado "Torta de Chocolate" habilitado.
+* Existe una categoria final habilitada llamada "Tortas de Chocolate".</t>
+  </si>
+  <si>
+    <t>* Existe un producto llamado "Torta de Chocolate" deshabilitado.
+* Existe una categoria final habilitada llamada "Tortas de Chocolate".</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -559,11 +563,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -691,29 +695,29 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -849,23 +853,23 @@
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -875,7 +879,7 @@
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -1013,23 +1017,23 @@
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -1039,7 +1043,7 @@
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -1177,23 +1181,23 @@
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -1203,7 +1207,7 @@
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -1396,7 +1400,9 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1484,7 +1490,9 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -1560,9 +1568,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1650,9 +1656,7 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -1728,42 +1732,36 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1892,36 +1890,42 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -2542,7 +2546,9 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -2630,7 +2636,9 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -2874,9 +2882,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -2964,9 +2970,7 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -2987,23 +2991,23 @@
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -3013,7 +3017,7 @@
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -3067,75 +3071,75 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ED63C8F8-D37D-47CE-8ABD-CD0B4463535B}" name="Table237" displayName="Table237" ref="A7:E12" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ED63C8F8-D37D-47CE-8ABD-CD0B4463535B}" name="Table237" displayName="Table237" ref="A7:E12" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
   <autoFilter ref="A7:E12" xr:uid="{C90AE16F-5A5B-4C33-98F9-81888664F067}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{AA442F05-005C-40A9-AF0E-840349970DA6}" name="Numero de Paso" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{9BA3DA2D-A64B-49FD-84F5-8B9CECDA8C94}" name="Accion" dataDxfId="53"/>
-    <tableColumn id="8" xr3:uid="{7398C574-FB08-460A-A65C-353BEBED56AA}" name="Entrada" dataDxfId="52">
+    <tableColumn id="1" xr3:uid="{AA442F05-005C-40A9-AF0E-840349970DA6}" name="Numero de Paso" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{9BA3DA2D-A64B-49FD-84F5-8B9CECDA8C94}" name="Accion" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{7398C574-FB08-460A-A65C-353BEBED56AA}" name="Entrada" dataDxfId="42">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{941E312F-F05B-429C-AB3D-90CF6EBCE95F}" name="Resultados Esperados" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{640ED3EC-3D10-4853-8009-D804778E1055}" name="Resultados Obtenidos" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{941E312F-F05B-429C-AB3D-90CF6EBCE95F}" name="Resultados Esperados" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{640ED3EC-3D10-4853-8009-D804778E1055}" name="Resultados Obtenidos" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{49F79B8B-08F5-4AB8-8D1B-1DDF7D526A39}" name="Table23711" displayName="Table23711" ref="A7:E12" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{49F79B8B-08F5-4AB8-8D1B-1DDF7D526A39}" name="Table23711" displayName="Table23711" ref="A7:E12" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36" totalsRowBorderDxfId="35">
   <autoFilter ref="A7:E12" xr:uid="{047A055C-AF14-422C-8FB3-A5F122E33821}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{71B3CDAA-B918-4BCA-8198-1506AA5B8403}" name="Numero de Paso" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{C9FDA1F6-771C-401E-B2B8-CFB5782D5C0E}" name="Accion" dataDxfId="43"/>
-    <tableColumn id="8" xr3:uid="{1CBA1EAE-64C5-42C3-9598-C1F89C90CF37}" name="Entrada" dataDxfId="42">
+    <tableColumn id="1" xr3:uid="{71B3CDAA-B918-4BCA-8198-1506AA5B8403}" name="Numero de Paso" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{C9FDA1F6-771C-401E-B2B8-CFB5782D5C0E}" name="Accion" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{1CBA1EAE-64C5-42C3-9598-C1F89C90CF37}" name="Entrada" dataDxfId="32">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{995A4BB6-32D9-4A09-BDC0-63C82DD67204}" name="Resultados Esperados" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{10197ADB-2E56-4276-8430-52F0FE788BE3}" name="Resultados Obtenidos" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{995A4BB6-32D9-4A09-BDC0-63C82DD67204}" name="Resultados Esperados" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{10197ADB-2E56-4276-8430-52F0FE788BE3}" name="Resultados Obtenidos" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{CA7E955E-0A86-4947-B5C6-2613E55F6518}" name="Table237113" displayName="Table237113" ref="A7:E12" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36" totalsRowBorderDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{CA7E955E-0A86-4947-B5C6-2613E55F6518}" name="Table237113" displayName="Table237113" ref="A7:E12" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
   <autoFilter ref="A7:E12" xr:uid="{047A055C-AF14-422C-8FB3-A5F122E33821}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{69635C28-33DC-4282-AC1B-B502C94BEA3F}" name="Numero de Paso" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{55FDD76C-5C72-42A1-8794-690B8A92F318}" name="Accion" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{3C3840B1-1401-479C-84D3-436E5D745040}" name="Entrada" dataDxfId="32">
+    <tableColumn id="1" xr3:uid="{69635C28-33DC-4282-AC1B-B502C94BEA3F}" name="Numero de Paso" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{55FDD76C-5C72-42A1-8794-690B8A92F318}" name="Accion" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{3C3840B1-1401-479C-84D3-436E5D745040}" name="Entrada" dataDxfId="22">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3835C49B-BA3E-4A92-8F9D-95908326A3AC}" name="Resultados Esperados" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{3302F39D-C94D-4D64-9A08-BDAFF33AFF3B}" name="Resultados Obtenidos" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{3835C49B-BA3E-4A92-8F9D-95908326A3AC}" name="Resultados Esperados" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{3302F39D-C94D-4D64-9A08-BDAFF33AFF3B}" name="Resultados Obtenidos" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{6CA2A938-6402-4F0E-9A05-83B05A07661E}" name="Table2312" displayName="Table2312" ref="A7:E12" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{6CA2A938-6402-4F0E-9A05-83B05A07661E}" name="Table2312" displayName="Table2312" ref="A7:E12" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A7:E12" xr:uid="{25F65397-1E5C-40A2-8FC2-BB0E208A177E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{72CA698B-5567-4FE9-BE4A-5F369193357D}" name="Numero de Paso" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{E92C36AB-D96C-4146-A28D-E74F33897E00}" name="Accion" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{468D170D-611A-46E4-9012-22E2C94BD306}" name="Entrada" dataDxfId="22">
+    <tableColumn id="1" xr3:uid="{72CA698B-5567-4FE9-BE4A-5F369193357D}" name="Numero de Paso" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{E92C36AB-D96C-4146-A28D-E74F33897E00}" name="Accion" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{468D170D-611A-46E4-9012-22E2C94BD306}" name="Entrada" dataDxfId="12">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{2DDEC849-A79A-40F3-8BFA-F1A3D5ED281A}" name="Resultados Esperados" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{38B93C53-6888-4BD8-936A-340E074515FF}" name="Resultados Obtenidos" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{2DDEC849-A79A-40F3-8BFA-F1A3D5ED281A}" name="Resultados Esperados" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{38B93C53-6888-4BD8-936A-340E074515FF}" name="Resultados Obtenidos" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E523467A-E8B6-4FF2-8C8F-3CDCDB05E1F9}" name="Table231214" displayName="Table231214" ref="A7:E12" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E523467A-E8B6-4FF2-8C8F-3CDCDB05E1F9}" name="Table231214" displayName="Table231214" ref="A7:E12" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A7:E12" xr:uid="{E85131F1-E4F8-4567-9E28-46F38594088C}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{96C7221F-0868-45C1-B43C-AE675BFB9E1C}" name="Numero de Paso" dataDxfId="4"/>
@@ -3152,153 +3156,153 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{3FF9DF0C-32BE-4347-984C-A09794CCD4F2}" name="Table231214217" displayName="Table231214217" ref="A7:E11" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{3FF9DF0C-32BE-4347-984C-A09794CCD4F2}" name="Table231214217" displayName="Table231214217" ref="A7:E11" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146" totalsRowBorderDxfId="145">
   <autoFilter ref="A7:E11" xr:uid="{E85131F1-E4F8-4567-9E28-46F38594088C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4324B215-E039-4F8E-BDCE-B13F8FC97B83}" name="Numero de Paso" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{604AE212-AB7F-466A-846D-5851418040AB}" name="Accion" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{707791EE-F2EB-4590-B328-93D7258BD8AE}" name="Entrada" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{4324B215-E039-4F8E-BDCE-B13F8FC97B83}" name="Numero de Paso" dataDxfId="144"/>
+    <tableColumn id="2" xr3:uid="{604AE212-AB7F-466A-846D-5851418040AB}" name="Accion" dataDxfId="143"/>
+    <tableColumn id="8" xr3:uid="{707791EE-F2EB-4590-B328-93D7258BD8AE}" name="Entrada" dataDxfId="142">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F3B23BB8-D37A-4239-AF1B-DC05FAA1CAE9}" name="Resultados" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{F187C750-B74D-4FF9-8E3E-1783F252F0C7}" name="Comentarios" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{F3B23BB8-D37A-4239-AF1B-DC05FAA1CAE9}" name="Resultados" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{F187C750-B74D-4FF9-8E3E-1783F252F0C7}" name="Comentarios" dataDxfId="140"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3FAAF92A-2C8D-40DC-8A23-DD6A81E81F02}" name="Table215" displayName="Table215" ref="A7:E10" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146" totalsRowBorderDxfId="145">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3FAAF92A-2C8D-40DC-8A23-DD6A81E81F02}" name="Table215" displayName="Table215" ref="A7:E10" totalsRowShown="0" headerRowDxfId="129" dataDxfId="127" headerRowBorderDxfId="128" tableBorderDxfId="126" totalsRowBorderDxfId="125">
   <autoFilter ref="A7:E10" xr:uid="{3FAAF92A-2C8D-40DC-8A23-DD6A81E81F02}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{27A0B040-AA3E-4B05-8B4F-0EA2E64AE54A}" name="Numero de Paso" dataDxfId="144"/>
-    <tableColumn id="2" xr3:uid="{9E9176B7-2B18-4676-B8FF-05D61600B85F}" name="Accion" dataDxfId="143"/>
-    <tableColumn id="8" xr3:uid="{53F450CC-4F2B-4194-A7EA-4264D1CB2C45}" name="Entrada" dataDxfId="142">
+    <tableColumn id="1" xr3:uid="{27A0B040-AA3E-4B05-8B4F-0EA2E64AE54A}" name="Numero de Paso" dataDxfId="124"/>
+    <tableColumn id="2" xr3:uid="{9E9176B7-2B18-4676-B8FF-05D61600B85F}" name="Accion" dataDxfId="123"/>
+    <tableColumn id="8" xr3:uid="{53F450CC-4F2B-4194-A7EA-4264D1CB2C45}" name="Entrada" dataDxfId="122">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7481430F-57D2-4BB4-83FA-DF2B69ED8D12}" name="Resultados Esperados" dataDxfId="141"/>
-    <tableColumn id="6" xr3:uid="{826F56AE-21A3-4821-AC1F-046FE9FB74C6}" name="Resultados Obtenidos" dataDxfId="140"/>
+    <tableColumn id="5" xr3:uid="{7481430F-57D2-4BB4-83FA-DF2B69ED8D12}" name="Resultados Esperados" dataDxfId="121"/>
+    <tableColumn id="6" xr3:uid="{826F56AE-21A3-4821-AC1F-046FE9FB74C6}" name="Resultados Obtenidos" dataDxfId="120"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A69AFDA7-5333-4DFC-BE3B-ED11672B77E0}" name="Table23" displayName="Table23" ref="A7:E11" totalsRowShown="0" headerRowDxfId="129" dataDxfId="127" headerRowBorderDxfId="128" tableBorderDxfId="126" totalsRowBorderDxfId="125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A69AFDA7-5333-4DFC-BE3B-ED11672B77E0}" name="Table23" displayName="Table23" ref="A7:E11" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116" totalsRowBorderDxfId="115">
   <autoFilter ref="A7:E11" xr:uid="{A69AFDA7-5333-4DFC-BE3B-ED11672B77E0}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{56575A38-6385-4E32-959E-6FADA7A1B9DC}" name="Numero de Paso" dataDxfId="124"/>
-    <tableColumn id="2" xr3:uid="{0124314F-8F45-4DBF-865A-B9AFE3F427A5}" name="Accion" dataDxfId="123"/>
-    <tableColumn id="8" xr3:uid="{AD0A20D1-6635-486A-B087-CF3ADCB154A2}" name="Entrada" dataDxfId="122">
+    <tableColumn id="1" xr3:uid="{56575A38-6385-4E32-959E-6FADA7A1B9DC}" name="Numero de Paso" dataDxfId="114"/>
+    <tableColumn id="2" xr3:uid="{0124314F-8F45-4DBF-865A-B9AFE3F427A5}" name="Accion" dataDxfId="113"/>
+    <tableColumn id="8" xr3:uid="{AD0A20D1-6635-486A-B087-CF3ADCB154A2}" name="Entrada" dataDxfId="112">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{170FE1DC-9E41-476B-8831-18B106327E5A}" name="Resultados Esperados" dataDxfId="121"/>
-    <tableColumn id="6" xr3:uid="{4BDEDFFA-E9AA-47B7-AAB2-C58571DD752B}" name="Resultados Obtenidos" dataDxfId="120"/>
+    <tableColumn id="5" xr3:uid="{170FE1DC-9E41-476B-8831-18B106327E5A}" name="Resultados Esperados" dataDxfId="111"/>
+    <tableColumn id="6" xr3:uid="{4BDEDFFA-E9AA-47B7-AAB2-C58571DD752B}" name="Resultados Obtenidos" dataDxfId="110"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C9423D3B-2AA7-4E84-BBB2-F3328569400B}" name="Table234" displayName="Table234" ref="A7:E11" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116" totalsRowBorderDxfId="115">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C9423D3B-2AA7-4E84-BBB2-F3328569400B}" name="Table234" displayName="Table234" ref="A7:E11" totalsRowShown="0" headerRowDxfId="109" dataDxfId="107" headerRowBorderDxfId="108" tableBorderDxfId="106" totalsRowBorderDxfId="105">
   <autoFilter ref="A7:E11" xr:uid="{C9423D3B-2AA7-4E84-BBB2-F3328569400B}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{56BB9DBC-E6D5-49A0-B2E9-694579D4C3FA}" name="Numero de Paso" dataDxfId="114"/>
-    <tableColumn id="2" xr3:uid="{AF257FE1-E9A7-4805-9759-289F9009A053}" name="Accion" dataDxfId="113"/>
-    <tableColumn id="8" xr3:uid="{F0AC7AA4-24CA-4684-AD34-22BF35C4CE7E}" name="Entrada" dataDxfId="112">
+    <tableColumn id="1" xr3:uid="{56BB9DBC-E6D5-49A0-B2E9-694579D4C3FA}" name="Numero de Paso" dataDxfId="104"/>
+    <tableColumn id="2" xr3:uid="{AF257FE1-E9A7-4805-9759-289F9009A053}" name="Accion" dataDxfId="103"/>
+    <tableColumn id="8" xr3:uid="{F0AC7AA4-24CA-4684-AD34-22BF35C4CE7E}" name="Entrada" dataDxfId="102">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FE1F4107-6A10-4963-AB5C-51478CA94F97}" name="Resultados Esperados" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{02AC2EF7-7893-49B7-89E8-98D398EBC720}" name="Resultados Obtenidos" dataDxfId="110"/>
+    <tableColumn id="5" xr3:uid="{FE1F4107-6A10-4963-AB5C-51478CA94F97}" name="Resultados Esperados" dataDxfId="101"/>
+    <tableColumn id="6" xr3:uid="{02AC2EF7-7893-49B7-89E8-98D398EBC720}" name="Resultados Obtenidos" dataDxfId="100"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4D7FFC4A-D03E-437C-ABEC-D1BEE1516B9E}" name="Table2345" displayName="Table2345" ref="A7:E11" totalsRowShown="0" headerRowDxfId="109" dataDxfId="107" headerRowBorderDxfId="108" tableBorderDxfId="106" totalsRowBorderDxfId="105">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4D7FFC4A-D03E-437C-ABEC-D1BEE1516B9E}" name="Table2345" displayName="Table2345" ref="A7:E11" totalsRowShown="0" headerRowDxfId="99" dataDxfId="97" headerRowBorderDxfId="98" tableBorderDxfId="96" totalsRowBorderDxfId="95">
   <autoFilter ref="A7:E11" xr:uid="{4D7FFC4A-D03E-437C-ABEC-D1BEE1516B9E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9647289F-3F7D-4E9D-A95D-56095B2F12C5}" name="Numero de Paso" dataDxfId="104"/>
-    <tableColumn id="2" xr3:uid="{E589E827-D06E-4E49-96F2-C0B6031E5515}" name="Accion" dataDxfId="103"/>
-    <tableColumn id="8" xr3:uid="{63D171B5-892A-49D1-887F-844CDE9AE276}" name="Entrada" dataDxfId="102">
+    <tableColumn id="1" xr3:uid="{9647289F-3F7D-4E9D-A95D-56095B2F12C5}" name="Numero de Paso" dataDxfId="94"/>
+    <tableColumn id="2" xr3:uid="{E589E827-D06E-4E49-96F2-C0B6031E5515}" name="Accion" dataDxfId="93"/>
+    <tableColumn id="8" xr3:uid="{63D171B5-892A-49D1-887F-844CDE9AE276}" name="Entrada" dataDxfId="92">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5A27459D-3213-49DA-BF0F-EB708CC8FEE2}" name="Resultados Esperados" dataDxfId="101"/>
-    <tableColumn id="6" xr3:uid="{C759DDEF-3E5A-45DA-8FCC-843592A2910E}" name="Resultados Obtenidos" dataDxfId="100"/>
+    <tableColumn id="5" xr3:uid="{5A27459D-3213-49DA-BF0F-EB708CC8FEE2}" name="Resultados Esperados" dataDxfId="91"/>
+    <tableColumn id="6" xr3:uid="{C759DDEF-3E5A-45DA-8FCC-843592A2910E}" name="Resultados Obtenidos" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{70D06BD0-4AAC-42FB-B65A-C57E36ABD004}" name="Table23458" displayName="Table23458" ref="A7:E11" totalsRowShown="0" headerRowDxfId="99" dataDxfId="97" headerRowBorderDxfId="98" tableBorderDxfId="96" totalsRowBorderDxfId="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{70D06BD0-4AAC-42FB-B65A-C57E36ABD004}" name="Table23458" displayName="Table23458" ref="A7:E11" totalsRowShown="0" headerRowDxfId="89" dataDxfId="87" headerRowBorderDxfId="88" tableBorderDxfId="86" totalsRowBorderDxfId="85">
   <autoFilter ref="A7:E11" xr:uid="{70D06BD0-4AAC-42FB-B65A-C57E36ABD004}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B66041C0-EDAE-496F-977E-2AFE26696DC1}" name="Numero de Paso" dataDxfId="94"/>
-    <tableColumn id="2" xr3:uid="{5EDA8EC9-7061-4CAE-AF66-4155B5EA70C9}" name="Accion" dataDxfId="93"/>
-    <tableColumn id="8" xr3:uid="{0673BD94-FA92-4034-B9FE-2C86D2F3D419}" name="Entrada" dataDxfId="92">
+    <tableColumn id="1" xr3:uid="{B66041C0-EDAE-496F-977E-2AFE26696DC1}" name="Numero de Paso" dataDxfId="84"/>
+    <tableColumn id="2" xr3:uid="{5EDA8EC9-7061-4CAE-AF66-4155B5EA70C9}" name="Accion" dataDxfId="83"/>
+    <tableColumn id="8" xr3:uid="{0673BD94-FA92-4034-B9FE-2C86D2F3D419}" name="Entrada" dataDxfId="82">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6D165DBB-FC7C-45EC-8AA3-BDDC46419C74}" name="Resultados Esperados" dataDxfId="91"/>
-    <tableColumn id="6" xr3:uid="{2710CB00-6980-488D-9027-F2E32E562C3E}" name="Resultados Obtenidos" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{6D165DBB-FC7C-45EC-8AA3-BDDC46419C74}" name="Resultados Esperados" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{2710CB00-6980-488D-9027-F2E32E562C3E}" name="Resultados Obtenidos" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{B6E49E3B-2594-4373-A9E8-31405D197DB6}" name="Table234589" displayName="Table234589" ref="A7:E11" totalsRowShown="0" headerRowDxfId="89" dataDxfId="87" headerRowBorderDxfId="88" tableBorderDxfId="86" totalsRowBorderDxfId="85">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{B6E49E3B-2594-4373-A9E8-31405D197DB6}" name="Table234589" displayName="Table234589" ref="A7:E11" totalsRowShown="0" headerRowDxfId="79" dataDxfId="77" headerRowBorderDxfId="78" tableBorderDxfId="76" totalsRowBorderDxfId="75">
   <autoFilter ref="A7:E11" xr:uid="{B6E49E3B-2594-4373-A9E8-31405D197DB6}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E3B76354-6614-4EC1-BB24-34C199C49138}" name="Numero de Paso" dataDxfId="84"/>
-    <tableColumn id="2" xr3:uid="{CE6F728F-E377-4600-8610-0823232D3C20}" name="Accion" dataDxfId="83"/>
-    <tableColumn id="8" xr3:uid="{EDC41109-1C52-45FD-AC32-EFEF87CB908C}" name="Entrada" dataDxfId="82">
+    <tableColumn id="1" xr3:uid="{E3B76354-6614-4EC1-BB24-34C199C49138}" name="Numero de Paso" dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{CE6F728F-E377-4600-8610-0823232D3C20}" name="Accion" dataDxfId="73"/>
+    <tableColumn id="8" xr3:uid="{EDC41109-1C52-45FD-AC32-EFEF87CB908C}" name="Entrada" dataDxfId="72">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{10D03F6A-3B48-4B4C-AB1F-7C834555A22F}" name="Resultados Esperados" dataDxfId="81"/>
-    <tableColumn id="6" xr3:uid="{77D52C61-7D1E-4505-879C-C2D7C8374B79}" name="Resultados Obtenidos" dataDxfId="80"/>
+    <tableColumn id="5" xr3:uid="{10D03F6A-3B48-4B4C-AB1F-7C834555A22F}" name="Resultados Esperados" dataDxfId="71"/>
+    <tableColumn id="6" xr3:uid="{77D52C61-7D1E-4505-879C-C2D7C8374B79}" name="Resultados Obtenidos" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{815EF42E-D784-4219-AD3C-9AC949D530D1}" name="Table236" displayName="Table236" ref="A7:E12" totalsRowShown="0" headerRowDxfId="79" dataDxfId="77" headerRowBorderDxfId="78" tableBorderDxfId="76" totalsRowBorderDxfId="75">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{815EF42E-D784-4219-AD3C-9AC949D530D1}" name="Table236" displayName="Table236" ref="A7:E12" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68" tableBorderDxfId="66" totalsRowBorderDxfId="65">
   <autoFilter ref="A7:E12" xr:uid="{715B9BAD-1497-41F0-B764-45044D3C92AC}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A93CF38D-7DFE-4F9A-9377-898DFF943F87}" name="Numero de Paso" dataDxfId="74"/>
-    <tableColumn id="2" xr3:uid="{0702067E-FD3D-44DC-9E82-1D0504306ED4}" name="Accion" dataDxfId="73"/>
-    <tableColumn id="8" xr3:uid="{7C9F77C2-31E9-4117-A7A2-F7356C3FC7AE}" name="Entrada" dataDxfId="72">
+    <tableColumn id="1" xr3:uid="{A93CF38D-7DFE-4F9A-9377-898DFF943F87}" name="Numero de Paso" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{0702067E-FD3D-44DC-9E82-1D0504306ED4}" name="Accion" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{7C9F77C2-31E9-4117-A7A2-F7356C3FC7AE}" name="Entrada" dataDxfId="62">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7AD3CC43-D1D7-4195-9746-65A7A8FD220B}" name="Resultados Esperados" dataDxfId="71"/>
-    <tableColumn id="6" xr3:uid="{986A7CE9-EF2E-40D3-A217-09C2FB7B25F3}" name="Resultados Obtenidos" dataDxfId="70"/>
+    <tableColumn id="5" xr3:uid="{7AD3CC43-D1D7-4195-9746-65A7A8FD220B}" name="Resultados Esperados" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{986A7CE9-EF2E-40D3-A217-09C2FB7B25F3}" name="Resultados Obtenidos" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{F7D47040-4A05-469E-8772-1E419830AEB8}" name="Table21516" displayName="Table21516" ref="A7:E10" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68" tableBorderDxfId="66" totalsRowBorderDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{F7D47040-4A05-469E-8772-1E419830AEB8}" name="Table21516" displayName="Table21516" ref="A7:E10" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
   <autoFilter ref="A7:E10" xr:uid="{F7D47040-4A05-469E-8772-1E419830AEB8}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F771E58E-D809-4572-8829-3A29D4FCE3F4}" name="Numero de Paso" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{B6101E35-03D2-49CE-B842-062C4A8AE380}" name="Accion" dataDxfId="63"/>
-    <tableColumn id="8" xr3:uid="{D94708F2-1E8F-4E64-AC2B-1D38C72768E1}" name="Entrada" dataDxfId="62">
+    <tableColumn id="1" xr3:uid="{F771E58E-D809-4572-8829-3A29D4FCE3F4}" name="Numero de Paso" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{B6101E35-03D2-49CE-B842-062C4A8AE380}" name="Accion" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{D94708F2-1E8F-4E64-AC2B-1D38C72768E1}" name="Entrada" dataDxfId="52">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{563F58D4-687D-4394-B151-C791528C0ECF}" name="Resultados Esperados" dataDxfId="61"/>
-    <tableColumn id="6" xr3:uid="{B9462076-3482-4FF0-8B86-2B5D3DE49305}" name="Resultados Obtenidos" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{563F58D4-687D-4394-B151-C791528C0ECF}" name="Resultados Esperados" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{B9462076-3482-4FF0-8B86-2B5D3DE49305}" name="Resultados Obtenidos" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3622,16 +3626,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7464F8-FD2A-4AA0-91F8-5070CACB58B0}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="48.42578125" customWidth="1"/>
-    <col min="4" max="4" width="39.5703125" customWidth="1"/>
-    <col min="5" max="5" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="48.375" customWidth="1"/>
+    <col min="4" max="4" width="39.625" customWidth="1"/>
+    <col min="5" max="5" width="28.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -3640,7 +3644,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -3655,11 +3659,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:5" ht="23.1" customHeight="1">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="6" t="s">
         <v>21</v>
       </c>
@@ -3670,11 +3674,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:5" ht="81" customHeight="1">
+      <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
         <v>18</v>
       </c>
@@ -3685,23 +3689,23 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:5" ht="15" customHeight="1">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -3718,7 +3722,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="42.75">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -3733,7 +3737,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -3748,7 +3752,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="90.75" customHeight="1">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -3763,7 +3767,7 @@
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="73.5" customHeight="1">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -3796,15 +3800,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C94357D-4B8B-4069-8E95-5BA7D552E10A}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="44.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.625" customWidth="1"/>
+    <col min="3" max="3" width="44.875" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" customWidth="1"/>
+    <col min="5" max="5" width="31.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -3813,7 +3817,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -3825,14 +3829,14 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="23.1" customHeight="1">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="6" t="s">
         <v>47</v>
       </c>
@@ -3843,13 +3847,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:5" ht="90" customHeight="1">
+      <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
@@ -3858,23 +3862,23 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -3891,7 +3895,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="109.5" customHeight="1">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -3906,37 +3910,37 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="42.75">
       <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="42.75">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="71.25">
       <c r="A11" s="14">
         <v>4</v>
       </c>
@@ -3944,14 +3948,14 @@
         <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="85.5">
       <c r="A12" s="10">
         <v>5</v>
       </c>
@@ -3962,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -3984,15 +3988,15 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE0B44F7-6594-44AE-870D-EDB2D5C8327F}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -4001,7 +4005,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -4013,14 +4017,14 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36.950000000000003" customHeight="1">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="4" t="s">
         <v>48</v>
       </c>
@@ -4031,13 +4035,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:5" ht="67.5" customHeight="1">
+      <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
@@ -4046,23 +4050,23 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -4079,7 +4083,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="87.75" customHeight="1">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -4094,37 +4098,37 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="28.5">
       <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="28.5">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="85.5">
       <c r="A11" s="14">
         <v>4</v>
       </c>
@@ -4132,14 +4136,14 @@
         <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="57">
       <c r="A12" s="10">
         <v>5</v>
       </c>
@@ -4150,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -4172,15 +4176,15 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD4039FB-637D-41B4-9D1F-D9255627A80E}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -4189,7 +4193,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -4201,14 +4205,14 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36.950000000000003" customHeight="1">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="4" t="s">
         <v>48</v>
       </c>
@@ -4219,13 +4223,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:5" ht="85.5">
+      <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
@@ -4234,23 +4238,23 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -4267,7 +4271,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="87.75" customHeight="1">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -4282,37 +4286,37 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="28.5">
       <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="28.5">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="85.5">
       <c r="A11" s="14">
         <v>4</v>
       </c>
@@ -4327,7 +4331,7 @@
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="57">
       <c r="A12" s="10">
         <v>5</v>
       </c>
@@ -4338,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -4360,15 +4364,15 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729CB741-417B-40AD-BC21-C3249BB6C4E1}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="37.42578125" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" customWidth="1"/>
-    <col min="4" max="4" width="29.140625" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="37.375" customWidth="1"/>
+    <col min="3" max="3" width="46.625" customWidth="1"/>
+    <col min="4" max="4" width="29.125" customWidth="1"/>
+    <col min="5" max="5" width="34.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -4377,7 +4381,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -4389,10 +4393,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="23.1" customHeight="1">
       <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
@@ -4407,13 +4411,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="67.5" customHeight="1">
       <c r="A4" s="16" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>8</v>
@@ -4422,23 +4426,23 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -4455,7 +4459,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="77.25" customHeight="1">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -4470,37 +4474,37 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="28.5">
       <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="63.75" customHeight="1">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="57">
       <c r="A11" s="14">
         <v>4</v>
       </c>
@@ -4508,14 +4512,14 @@
         <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="85.5">
       <c r="A12" s="10">
         <v>5</v>
       </c>
@@ -4526,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -4549,15 +4553,15 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43387705-F35A-43C8-B4A6-19D31406FDCE}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="47.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.375" customWidth="1"/>
+    <col min="3" max="3" width="47.875" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="5" width="48.7109375" customWidth="1"/>
+    <col min="5" max="5" width="48.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -4566,7 +4570,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -4578,10 +4582,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="23.1" customHeight="1">
       <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
@@ -4596,13 +4600,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="57">
       <c r="A4" s="16" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>8</v>
@@ -4611,23 +4615,23 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -4644,7 +4648,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="110.25" customHeight="1">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -4659,22 +4663,22 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="42.75">
       <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="63.75" customHeight="1">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -4685,11 +4689,11 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="57">
       <c r="A11" s="14">
         <v>4</v>
       </c>
@@ -4704,7 +4708,7 @@
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="71.25">
       <c r="A12" s="10">
         <v>5</v>
       </c>
@@ -4715,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -4737,15 +4741,15 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576B818F-F28E-40A4-B9A6-949AC65F1FEB}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.375" customWidth="1"/>
+    <col min="3" max="3" width="32.625" customWidth="1"/>
+    <col min="4" max="4" width="31.125" customWidth="1"/>
+    <col min="5" max="5" width="27.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -4754,7 +4758,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -4766,16 +4770,16 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.5">
       <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="4" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>11</v>
@@ -4784,38 +4788,38 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="57">
       <c r="A4" s="16" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -4832,7 +4836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="110.25" customHeight="1">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -4847,7 +4851,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="63.75" customHeight="1">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -4858,11 +4862,11 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="71.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -4870,14 +4874,14 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="85.5">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -4888,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -4910,16 +4914,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D3E5279-DE54-405E-8578-D6AEC7A646E7}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="45.5703125" customWidth="1"/>
-    <col min="4" max="4" width="34.28515625" customWidth="1"/>
-    <col min="5" max="5" width="32.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.625" customWidth="1"/>
+    <col min="2" max="2" width="29.375" customWidth="1"/>
+    <col min="3" max="3" width="45.625" customWidth="1"/>
+    <col min="4" max="4" width="34.25" customWidth="1"/>
+    <col min="5" max="5" width="32.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -4928,7 +4932,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -4943,11 +4947,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="6" t="s">
         <v>21</v>
       </c>
@@ -4958,11 +4962,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -4970,26 +4974,26 @@
         <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -5006,7 +5010,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="57">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -5021,7 +5025,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="28.5">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -5036,18 +5040,18 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="42.75">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" s="1"/>
     </row>
@@ -5069,18 +5073,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67E29C34-DF65-45B8-AD19-1DFC37FA57BB}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="38.140625" customWidth="1"/>
-    <col min="5" max="5" width="35.42578125" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="38.125" customWidth="1"/>
+    <col min="5" max="5" width="35.375" customWidth="1"/>
+    <col min="6" max="6" width="12.125" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="30.6" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -5091,7 +5095,7 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
     </row>
-    <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -5103,16 +5107,16 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
     </row>
-    <row r="3" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:7" ht="23.1" customHeight="1">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="6" t="s">
         <v>20</v>
       </c>
@@ -5125,11 +5129,11 @@
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
     </row>
-    <row r="4" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:7" ht="57" customHeight="1">
+      <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
         <v>39</v>
       </c>
@@ -5142,27 +5146,27 @@
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:7">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
+    <row r="6" spans="1:7">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -5181,7 +5185,7 @@
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
     </row>
-    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="42.75">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -5198,7 +5202,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="42.75">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -5215,7 +5219,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
     </row>
-    <row r="10" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="85.5">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -5232,7 +5236,7 @@
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="42.75">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -5267,16 +5271,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41B16007-58C5-48FC-8F60-85E556DEBCB4}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="45.28515625" customWidth="1"/>
-    <col min="4" max="4" width="29.42578125" customWidth="1"/>
-    <col min="5" max="5" width="41.7109375" customWidth="1"/>
+    <col min="1" max="1" width="24.25" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
+    <col min="3" max="3" width="45.25" customWidth="1"/>
+    <col min="4" max="4" width="29.375" customWidth="1"/>
+    <col min="5" max="5" width="41.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -5285,7 +5289,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -5297,14 +5301,14 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="45" customHeight="1">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="4" t="s">
         <v>22</v>
       </c>
@@ -5315,11 +5319,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:5" ht="85.5" customHeight="1">
+      <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
         <v>40</v>
       </c>
@@ -5330,23 +5334,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -5363,7 +5367,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="57">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -5378,7 +5382,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="28.5">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -5393,7 +5397,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="99.75">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -5408,7 +5412,7 @@
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="57">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -5441,15 +5445,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADF569A5-AED4-47B8-8460-E603D5D489B6}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
-    <col min="3" max="3" width="57.5703125" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.375" customWidth="1"/>
+    <col min="3" max="3" width="57.625" customWidth="1"/>
+    <col min="4" max="4" width="23.625" customWidth="1"/>
+    <col min="5" max="5" width="34.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -5458,7 +5462,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -5470,14 +5474,14 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="23.1" customHeight="1">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="4" t="s">
         <v>25</v>
       </c>
@@ -5488,11 +5492,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:5" ht="52.5" customHeight="1">
+      <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
         <v>24</v>
       </c>
@@ -5503,23 +5507,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -5536,7 +5540,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="115.5" customHeight="1">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -5551,7 +5555,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="74.25" customHeight="1">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -5566,7 +5570,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="85.5">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -5574,14 +5578,14 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="114">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -5592,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -5614,15 +5618,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4500079-5767-4667-A91F-52A8A3A10B11}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="43.140625" customWidth="1"/>
-    <col min="4" max="4" width="41.140625" customWidth="1"/>
-    <col min="5" max="5" width="34.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="43.125" customWidth="1"/>
+    <col min="4" max="4" width="41.125" customWidth="1"/>
+    <col min="5" max="5" width="34.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -5631,7 +5635,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -5643,14 +5647,14 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="32.25" customHeight="1">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="4" t="s">
         <v>26</v>
       </c>
@@ -5661,11 +5665,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:5" ht="84.75" customHeight="1">
+      <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
         <v>24</v>
       </c>
@@ -5676,23 +5680,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -5709,7 +5713,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="105" customHeight="1">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -5724,7 +5728,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="42.75">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -5739,7 +5743,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="99.75">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -5747,14 +5751,14 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="57">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -5765,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -5787,15 +5791,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7778A3F3-DDC3-4C3E-91B3-AA6F6F678769}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" customWidth="1"/>
+    <col min="2" max="2" width="29.75" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="5" max="5" width="23.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -5804,7 +5808,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -5816,14 +5820,14 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="76.5" customHeight="1">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="4" t="s">
         <v>27</v>
       </c>
@@ -5834,11 +5838,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:5" ht="81" customHeight="1">
+      <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
         <v>24</v>
       </c>
@@ -5849,23 +5853,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -5882,7 +5886,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="104.25" customHeight="1">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -5897,7 +5901,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="28.5">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -5912,7 +5916,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="128.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -5920,14 +5924,14 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="85.5">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -5938,7 +5942,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -5960,15 +5964,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49B773F1-27C7-44CC-8EC9-9C55B5034F40}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="25.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.25" customWidth="1"/>
     <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" customWidth="1"/>
+    <col min="5" max="5" width="24.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -5977,7 +5981,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -5992,11 +5996,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:5" ht="23.1" customHeight="1">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="6" t="s">
         <v>45</v>
       </c>
@@ -6007,38 +6011,38 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:5" ht="100.5" customHeight="1">
+      <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -6055,7 +6059,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="94.5" customHeight="1">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -6070,37 +6074,37 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="94.5" customHeight="1">
       <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="42.75">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="71.25">
       <c r="A11" s="14">
         <v>4</v>
       </c>
@@ -6108,14 +6112,14 @@
         <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="85.5">
       <c r="A12" s="10">
         <v>5</v>
       </c>
@@ -6126,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -6148,15 +6152,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7784B90-F395-403E-BE63-7627F1A8902A}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="40.85546875" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" customWidth="1"/>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="3" max="3" width="16.25" customWidth="1"/>
+    <col min="4" max="4" width="40.875" customWidth="1"/>
+    <col min="5" max="5" width="58.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
@@ -6165,7 +6169,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -6180,11 +6184,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="6" t="s">
         <v>21</v>
       </c>
@@ -6195,11 +6199,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -6207,26 +6211,26 @@
         <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -6243,7 +6247,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="42.75">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -6258,7 +6262,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="28.5">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -6269,22 +6273,22 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="42.75">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" s="1"/>
     </row>

--- a/IngSoftware/propuesta/CasosDeTests/CasosTest-Gestionar Producto.xlsx
+++ b/IngSoftware/propuesta/CasosDeTests/CasosTest-Gestionar Producto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eerojas\source\TrabajoFinalAus\IngSoftware\propuesta\CasosDeTests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CFD622C-6E5B-41CF-B174-D3D1DD932EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0FCA68-EF5A-4AC7-839D-09E5D4C76FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="13" xr2:uid="{907B4683-9A02-4D8C-B9E2-85A5E705A97A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="14" xr2:uid="{907B4683-9A02-4D8C-B9E2-85A5E705A97A}"/>
   </bookViews>
   <sheets>
     <sheet name="7A-CASO FELIZ" sheetId="1" r:id="rId1"/>
@@ -243,9 +243,6 @@
     <t>El Producto se modifica y queda deshabilitado.</t>
   </si>
   <si>
-    <t>Modificacion de  Producto: Baja de producto.</t>
-  </si>
-  <si>
     <t>Se abre un nuevo formulario para realizar la modificacion del producto.</t>
   </si>
   <si>
@@ -422,12 +419,15 @@
     <t>* Existe un producto llamado "Torta de Chocolate" deshabilitado.
 * Existe una categoria final habilitada llamada "Tortas de Chocolate".</t>
   </si>
+  <si>
+    <t>Modificacion de  Producto: Deshabilitar producto.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -557,11 +557,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -689,23 +689,23 @@
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -715,7 +715,7 @@
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -2991,23 +2991,23 @@
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -3017,7 +3017,7 @@
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -3139,34 +3139,34 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E523467A-E8B6-4FF2-8C8F-3CDCDB05E1F9}" name="Table231214" displayName="Table231214" ref="A7:E12" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E523467A-E8B6-4FF2-8C8F-3CDCDB05E1F9}" name="Table231214" displayName="Table231214" ref="A7:E12" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146" totalsRowBorderDxfId="145">
   <autoFilter ref="A7:E12" xr:uid="{E85131F1-E4F8-4567-9E28-46F38594088C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{96C7221F-0868-45C1-B43C-AE675BFB9E1C}" name="Numero de Paso" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{63E5C869-25BF-41CC-95B4-3A1DBC1F2679}" name="Accion" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{D0357635-7DA4-4723-8FCA-29E6A91BB2B8}" name="Entrada" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{96C7221F-0868-45C1-B43C-AE675BFB9E1C}" name="Numero de Paso" dataDxfId="144"/>
+    <tableColumn id="2" xr3:uid="{63E5C869-25BF-41CC-95B4-3A1DBC1F2679}" name="Accion" dataDxfId="143"/>
+    <tableColumn id="8" xr3:uid="{D0357635-7DA4-4723-8FCA-29E6A91BB2B8}" name="Entrada" dataDxfId="142">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{09BD5A8E-411B-4D50-A50F-7DC071E009B2}" name="Resultados Esperados" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{3D19E504-2712-484C-92BD-DF8EDF1FF518}" name="Resultados Obtenidos" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{09BD5A8E-411B-4D50-A50F-7DC071E009B2}" name="Resultados Esperados" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{3D19E504-2712-484C-92BD-DF8EDF1FF518}" name="Resultados Obtenidos" dataDxfId="140"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{3FF9DF0C-32BE-4347-984C-A09794CCD4F2}" name="Table231214217" displayName="Table231214217" ref="A7:E11" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146" totalsRowBorderDxfId="145">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{3FF9DF0C-32BE-4347-984C-A09794CCD4F2}" name="Table231214217" displayName="Table231214217" ref="A7:E11" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A7:E11" xr:uid="{E85131F1-E4F8-4567-9E28-46F38594088C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4324B215-E039-4F8E-BDCE-B13F8FC97B83}" name="Numero de Paso" dataDxfId="144"/>
-    <tableColumn id="2" xr3:uid="{604AE212-AB7F-466A-846D-5851418040AB}" name="Accion" dataDxfId="143"/>
-    <tableColumn id="8" xr3:uid="{707791EE-F2EB-4590-B328-93D7258BD8AE}" name="Entrada" dataDxfId="142">
+    <tableColumn id="1" xr3:uid="{4324B215-E039-4F8E-BDCE-B13F8FC97B83}" name="Numero de Paso" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{604AE212-AB7F-466A-846D-5851418040AB}" name="Accion" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{707791EE-F2EB-4590-B328-93D7258BD8AE}" name="Entrada" dataDxfId="2">
       <calculatedColumnFormula array="1">- Nombre = "Torta de Chocolate"
 - Cantidad = "1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F3B23BB8-D37A-4239-AF1B-DC05FAA1CAE9}" name="Resultados" dataDxfId="141"/>
-    <tableColumn id="6" xr3:uid="{F187C750-B74D-4FF9-8E3E-1783F252F0C7}" name="Comentarios" dataDxfId="140"/>
+    <tableColumn id="5" xr3:uid="{F3B23BB8-D37A-4239-AF1B-DC05FAA1CAE9}" name="Resultados" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{F187C750-B74D-4FF9-8E3E-1783F252F0C7}" name="Comentarios" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3626,29 +3626,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7464F8-FD2A-4AA0-91F8-5070CACB58B0}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="48.375" customWidth="1"/>
-    <col min="4" max="4" width="39.625" customWidth="1"/>
-    <col min="5" max="5" width="28.25" customWidth="1"/>
+    <col min="3" max="3" width="48.42578125" customWidth="1"/>
+    <col min="4" max="4" width="39.5703125" customWidth="1"/>
+    <col min="5" max="5" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="23.1" customHeight="1">
+    <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="81" customHeight="1">
+    <row r="4" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1">
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -3698,14 +3698,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="42.75">
+    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="90.75" customHeight="1">
+    <row r="10" spans="1:5" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="73.5" customHeight="1">
+    <row r="11" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -3800,28 +3800,28 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C94357D-4B8B-4069-8E95-5BA7D552E10A}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.625" customWidth="1"/>
-    <col min="3" max="3" width="44.875" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="44.85546875" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="31.25" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -3829,10 +3829,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="23.1" customHeight="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -3847,13 +3847,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="90" customHeight="1">
+    <row r="4" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
@@ -3862,7 +3862,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -3871,14 +3871,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="109.5" customHeight="1">
+    <row r="8" spans="1:5" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -3910,37 +3910,37 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="42.75">
+    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="42.75">
+    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="71.25">
+    <row r="11" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>4</v>
       </c>
@@ -3948,14 +3948,14 @@
         <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="85.5">
+    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>5</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -3988,28 +3988,28 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE0B44F7-6594-44AE-870D-EDB2D5C8327F}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
-    <col min="5" max="5" width="18.125" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -4017,10 +4017,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="36.950000000000003" customHeight="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -4035,13 +4035,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="67.5" customHeight="1">
+    <row r="4" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
@@ -4050,7 +4050,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -4059,14 +4059,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="87.75" customHeight="1">
+    <row r="8" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -4098,37 +4098,37 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="28.5">
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="28.5">
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="85.5">
+    <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>4</v>
       </c>
@@ -4136,14 +4136,14 @@
         <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="57">
+    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>5</v>
       </c>
@@ -4154,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -4176,28 +4176,28 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD4039FB-637D-41B4-9D1F-D9255627A80E}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
-    <col min="5" max="5" width="18.125" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -4205,10 +4205,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="36.950000000000003" customHeight="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -4223,13 +4223,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="85.5">
+    <row r="4" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
@@ -4238,7 +4238,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -4247,14 +4247,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="87.75" customHeight="1">
+    <row r="8" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -4286,37 +4286,37 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="28.5">
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="28.5">
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="85.5">
+    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>4</v>
       </c>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="57">
+    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>5</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -4364,28 +4364,28 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729CB741-417B-40AD-BC21-C3249BB6C4E1}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.375" customWidth="1"/>
-    <col min="3" max="3" width="46.625" customWidth="1"/>
-    <col min="4" max="4" width="29.125" customWidth="1"/>
-    <col min="5" max="5" width="34.75" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" customWidth="1"/>
+    <col min="4" max="4" width="29.140625" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -4393,14 +4393,14 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A3" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="16"/>
+      <c r="B3" s="15"/>
       <c r="C3" s="6" t="s">
         <v>50</v>
       </c>
@@ -4411,13 +4411,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="67.5" customHeight="1">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="15"/>
       <c r="C4" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>8</v>
@@ -4426,7 +4426,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -4435,14 +4435,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="77.25" customHeight="1">
+    <row r="8" spans="1:5" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -4474,37 +4474,37 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="28.5">
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="63.75" customHeight="1">
+    <row r="10" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="57">
+    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>4</v>
       </c>
@@ -4512,14 +4512,14 @@
         <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="85.5">
+    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>5</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -4553,28 +4553,28 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43387705-F35A-43C8-B4A6-19D31406FDCE}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.375" customWidth="1"/>
-    <col min="3" max="3" width="47.875" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="47.85546875" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="5" width="48.75" customWidth="1"/>
+    <col min="5" max="5" width="48.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -4582,16 +4582,16 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A3" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="16"/>
+      <c r="B3" s="15"/>
       <c r="C3" s="6" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>11</v>
@@ -4600,13 +4600,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="57">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="15"/>
       <c r="C4" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>8</v>
@@ -4615,7 +4615,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -4624,14 +4624,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -4648,7 +4648,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="110.25" customHeight="1">
+    <row r="8" spans="1:5" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -4663,22 +4663,22 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="42.75">
+    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="63.75" customHeight="1">
+    <row r="10" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -4689,11 +4689,11 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="57">
+    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>4</v>
       </c>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="71.25">
+    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>5</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -4741,28 +4741,28 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576B818F-F28E-40A4-B9A6-949AC65F1FEB}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.375" customWidth="1"/>
-    <col min="3" max="3" width="32.625" customWidth="1"/>
-    <col min="4" max="4" width="31.125" customWidth="1"/>
-    <col min="5" max="5" width="27.875" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -4770,16 +4770,16 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.5">
-      <c r="A3" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="16"/>
+      <c r="B3" s="15"/>
       <c r="C3" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>11</v>
@@ -4788,22 +4788,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="57">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="15"/>
       <c r="C4" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -4812,14 +4812,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -4836,7 +4836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="110.25" customHeight="1">
+    <row r="8" spans="1:5" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="63.75" customHeight="1">
+    <row r="9" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -4862,11 +4862,11 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="71.25">
+    <row r="10" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -4874,14 +4874,14 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="85.5">
+    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -4914,29 +4914,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D3E5279-DE54-405E-8578-D6AEC7A646E7}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.625" customWidth="1"/>
-    <col min="2" max="2" width="29.375" customWidth="1"/>
-    <col min="3" max="3" width="45.625" customWidth="1"/>
-    <col min="4" max="4" width="34.25" customWidth="1"/>
-    <col min="5" max="5" width="32.875" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
@@ -4974,10 +4974,10 @@
         <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -4986,14 +4986,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="57">
+    <row r="8" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="28.5">
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -5040,18 +5040,18 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="42.75">
+    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10" s="1"/>
     </row>
@@ -5073,33 +5073,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67E29C34-DF65-45B8-AD19-1DFC37FA57BB}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.875" customWidth="1"/>
-    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="38.125" customWidth="1"/>
-    <col min="5" max="5" width="35.375" customWidth="1"/>
-    <col min="6" max="6" width="12.125" customWidth="1"/>
-    <col min="7" max="7" width="18.75" customWidth="1"/>
+    <col min="4" max="4" width="38.140625" customWidth="1"/>
+    <col min="5" max="5" width="35.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.6" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
     </row>
-    <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -5107,12 +5107,12 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
     </row>
-    <row r="3" spans="1:7" ht="23.1" customHeight="1">
+    <row r="3" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -5129,7 +5129,7 @@
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
     </row>
-    <row r="4" spans="1:7" ht="57" customHeight="1">
+    <row r="4" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
@@ -5146,7 +5146,7 @@
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -5157,7 +5157,7 @@
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -5166,7 +5166,7 @@
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -5185,7 +5185,7 @@
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
     </row>
-    <row r="8" spans="1:7" ht="42.75">
+    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -5202,7 +5202,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
     </row>
-    <row r="9" spans="1:7" ht="42.75">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -5219,7 +5219,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
     </row>
-    <row r="10" spans="1:7" ht="85.5">
+    <row r="10" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -5236,7 +5236,7 @@
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7" ht="42.75">
+    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -5271,29 +5271,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41B16007-58C5-48FC-8F60-85E556DEBCB4}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.25" customWidth="1"/>
-    <col min="2" max="2" width="21.875" customWidth="1"/>
-    <col min="3" max="3" width="45.25" customWidth="1"/>
-    <col min="4" max="4" width="29.375" customWidth="1"/>
-    <col min="5" max="5" width="41.75" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="45.28515625" customWidth="1"/>
+    <col min="4" max="4" width="29.42578125" customWidth="1"/>
+    <col min="5" max="5" width="41.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -5301,10 +5301,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="45" customHeight="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="85.5" customHeight="1">
+    <row r="4" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -5343,14 +5343,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="57">
+    <row r="8" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="28.5">
+    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="99.75">
+    <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="57">
+    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -5445,28 +5445,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADF569A5-AED4-47B8-8460-E603D5D489B6}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.375" customWidth="1"/>
-    <col min="3" max="3" width="57.625" customWidth="1"/>
-    <col min="4" max="4" width="23.625" customWidth="1"/>
-    <col min="5" max="5" width="34.75" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="57.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -5474,10 +5474,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="23.1" customHeight="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="52.5" customHeight="1">
+    <row r="4" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -5516,14 +5516,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="115.5" customHeight="1">
+    <row r="8" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="74.25" customHeight="1">
+    <row r="9" spans="1:5" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="85.5">
+    <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -5578,14 +5578,14 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="114">
+    <row r="11" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -5596,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -5618,28 +5618,28 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4500079-5767-4667-A91F-52A8A3A10B11}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
-    <col min="3" max="3" width="43.125" customWidth="1"/>
-    <col min="4" max="4" width="41.125" customWidth="1"/>
-    <col min="5" max="5" width="34.875" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" customWidth="1"/>
+    <col min="4" max="4" width="41.140625" customWidth="1"/>
+    <col min="5" max="5" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -5647,10 +5647,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="32.25" customHeight="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -5665,7 +5665,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="84.75" customHeight="1">
+    <row r="4" spans="1:5" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -5689,14 +5689,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="105" customHeight="1">
+    <row r="8" spans="1:5" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="42.75">
+    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="99.75">
+    <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -5751,14 +5751,14 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="57">
+    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -5769,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -5791,28 +5791,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7778A3F3-DDC3-4C3E-91B3-AA6F6F678769}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.75" customWidth="1"/>
-    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="23.375" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -5820,10 +5820,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="76.5" customHeight="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -5838,7 +5838,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="81" customHeight="1">
+    <row r="4" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -5862,14 +5862,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="104.25" customHeight="1">
+    <row r="8" spans="1:5" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="28.5">
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="128.25">
+    <row r="10" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
@@ -5924,14 +5924,14 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="85.5">
+    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -5942,7 +5942,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -5964,28 +5964,28 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49B773F1-27C7-44CC-8EC9-9C55B5034F40}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.25" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" customWidth="1"/>
     <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
-    <col min="5" max="5" width="24.125" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="23.1" customHeight="1">
+    <row r="3" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -6011,22 +6011,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="100.5" customHeight="1">
+    <row r="4" spans="1:5" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -6035,14 +6035,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -6059,7 +6059,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="94.5" customHeight="1">
+    <row r="8" spans="1:5" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -6074,37 +6074,37 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="94.5" customHeight="1">
+    <row r="9" spans="1:5" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="42.75">
+    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="71.25">
+    <row r="11" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>4</v>
       </c>
@@ -6112,14 +6112,14 @@
         <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="85.5">
+    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>5</v>
       </c>
@@ -6130,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -6152,28 +6152,28 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7784B90-F395-403E-BE63-7627F1A8902A}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.375" customWidth="1"/>
-    <col min="3" max="3" width="16.25" customWidth="1"/>
-    <col min="4" max="4" width="40.875" customWidth="1"/>
-    <col min="5" max="5" width="58.125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="40.85546875" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="4">
         <v>7</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -6199,7 +6199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
@@ -6211,10 +6211,10 @@
         <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -6223,14 +6223,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -6247,7 +6247,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="42.75">
+    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="28.5">
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>2</v>
       </c>
@@ -6273,22 +6273,22 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="42.75">
+    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10" s="1"/>
     </row>
